--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="312">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -948,6 +948,9 @@
   <si>
     <t>['22', '56']</t>
   </si>
+  <si>
+    <t>['6', '11', '90+1']</t>
+  </si>
 </sst>
 </file>
 
@@ -1308,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2054,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ4">
         <v>0.78</v>
@@ -3293,7 +3296,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3702,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ12">
         <v>1.5</v>
@@ -4117,7 +4120,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ14">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4529,7 +4532,7 @@
         <v>1</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5971,7 +5974,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -7410,7 +7413,7 @@
         <v>0.5</v>
       </c>
       <c r="AP30">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ30">
         <v>0.64</v>
@@ -8028,7 +8031,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ33">
         <v>2</v>
@@ -8649,7 +8652,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR36">
         <v>1.46</v>
@@ -11945,7 +11948,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ52">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR52">
         <v>1.92</v>
@@ -12148,7 +12151,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ53">
         <v>2.5</v>
@@ -12563,7 +12566,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -13384,7 +13387,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ59">
         <v>1.67</v>
@@ -14414,10 +14417,10 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ64">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR64">
         <v>1.02</v>
@@ -16886,7 +16889,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ76">
         <v>2.3</v>
@@ -17301,7 +17304,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR78">
         <v>1.31</v>
@@ -18122,7 +18125,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ82">
         <v>0.89</v>
@@ -18537,7 +18540,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ84">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -20594,7 +20597,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ94">
         <v>2.5</v>
@@ -22039,7 +22042,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ101">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22242,7 +22245,7 @@
         <v>2</v>
       </c>
       <c r="AP102">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ102">
         <v>2</v>
@@ -22657,7 +22660,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ104">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR104">
         <v>1.61</v>
@@ -23684,7 +23687,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ109">
         <v>0.64</v>
@@ -26571,7 +26574,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ123">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -27804,7 +27807,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ129">
         <v>1.2</v>
@@ -28013,7 +28016,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ130">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR130">
         <v>1.48</v>
@@ -29040,7 +29043,7 @@
         <v>1.2</v>
       </c>
       <c r="AP135">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ135">
         <v>1.56</v>
@@ -29867,7 +29870,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ139">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR139">
         <v>1.59</v>
@@ -30897,7 +30900,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ144">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -32130,7 +32133,7 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ150">
         <v>1.2</v>
@@ -32339,7 +32342,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ151">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR151">
         <v>1.42</v>
@@ -32542,7 +32545,7 @@
         <v>2</v>
       </c>
       <c r="AP152">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ152">
         <v>2.3</v>
@@ -36456,7 +36459,7 @@
         <v>1.43</v>
       </c>
       <c r="AP171">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ171">
         <v>1.56</v>
@@ -36871,7 +36874,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ173">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR173">
         <v>1.48</v>
@@ -37074,7 +37077,7 @@
         <v>1.22</v>
       </c>
       <c r="AP174">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ174">
         <v>1.2</v>
@@ -37901,7 +37904,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ178">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR178">
         <v>1.5</v>
@@ -39767,22 +39770,22 @@
         <v>2.78</v>
       </c>
       <c r="AU187">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV187">
         <v>5</v>
       </c>
       <c r="AW187">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX187">
+        <v>12</v>
+      </c>
+      <c r="AY187">
         <v>13</v>
       </c>
-      <c r="AY187">
-        <v>14</v>
-      </c>
       <c r="AZ187">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA187">
         <v>7</v>
@@ -39831,6 +39834,418 @@
       </c>
       <c r="BP187">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7492339</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45668.45833333334</v>
+      </c>
+      <c r="F188">
+        <v>20</v>
+      </c>
+      <c r="G188" t="s">
+        <v>72</v>
+      </c>
+      <c r="H188" t="s">
+        <v>78</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>2</v>
+      </c>
+      <c r="K188">
+        <v>2</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>3</v>
+      </c>
+      <c r="N188">
+        <v>4</v>
+      </c>
+      <c r="O188" t="s">
+        <v>163</v>
+      </c>
+      <c r="P188" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q188">
+        <v>2.75</v>
+      </c>
+      <c r="R188">
+        <v>2</v>
+      </c>
+      <c r="S188">
+        <v>4.75</v>
+      </c>
+      <c r="T188">
+        <v>1.53</v>
+      </c>
+      <c r="U188">
+        <v>2.38</v>
+      </c>
+      <c r="V188">
+        <v>3.5</v>
+      </c>
+      <c r="W188">
+        <v>1.29</v>
+      </c>
+      <c r="X188">
+        <v>11</v>
+      </c>
+      <c r="Y188">
+        <v>1.05</v>
+      </c>
+      <c r="Z188">
+        <v>2.25</v>
+      </c>
+      <c r="AA188">
+        <v>3.2</v>
+      </c>
+      <c r="AB188">
+        <v>3.4</v>
+      </c>
+      <c r="AC188">
+        <v>1.1</v>
+      </c>
+      <c r="AD188">
+        <v>7.5</v>
+      </c>
+      <c r="AE188">
+        <v>1.47</v>
+      </c>
+      <c r="AF188">
+        <v>2.75</v>
+      </c>
+      <c r="AG188">
+        <v>2.3</v>
+      </c>
+      <c r="AH188">
+        <v>1.55</v>
+      </c>
+      <c r="AI188">
+        <v>2.05</v>
+      </c>
+      <c r="AJ188">
+        <v>1.7</v>
+      </c>
+      <c r="AK188">
+        <v>1.25</v>
+      </c>
+      <c r="AL188">
+        <v>1.35</v>
+      </c>
+      <c r="AM188">
+        <v>1.72</v>
+      </c>
+      <c r="AN188">
+        <v>0.78</v>
+      </c>
+      <c r="AO188">
+        <v>0.44</v>
+      </c>
+      <c r="AP188">
+        <v>0.7</v>
+      </c>
+      <c r="AQ188">
+        <v>0.7</v>
+      </c>
+      <c r="AR188">
+        <v>0.97</v>
+      </c>
+      <c r="AS188">
+        <v>1.11</v>
+      </c>
+      <c r="AT188">
+        <v>2.08</v>
+      </c>
+      <c r="AU188">
+        <v>6</v>
+      </c>
+      <c r="AV188">
+        <v>7</v>
+      </c>
+      <c r="AW188">
+        <v>10</v>
+      </c>
+      <c r="AX188">
+        <v>8</v>
+      </c>
+      <c r="AY188">
+        <v>18</v>
+      </c>
+      <c r="AZ188">
+        <v>18</v>
+      </c>
+      <c r="BA188">
+        <v>9</v>
+      </c>
+      <c r="BB188">
+        <v>2</v>
+      </c>
+      <c r="BC188">
+        <v>11</v>
+      </c>
+      <c r="BD188">
+        <v>1.65</v>
+      </c>
+      <c r="BE188">
+        <v>6.5</v>
+      </c>
+      <c r="BF188">
+        <v>2.48</v>
+      </c>
+      <c r="BG188">
+        <v>1.3</v>
+      </c>
+      <c r="BH188">
+        <v>3.15</v>
+      </c>
+      <c r="BI188">
+        <v>1.52</v>
+      </c>
+      <c r="BJ188">
+        <v>2.33</v>
+      </c>
+      <c r="BK188">
+        <v>1.85</v>
+      </c>
+      <c r="BL188">
+        <v>1.83</v>
+      </c>
+      <c r="BM188">
+        <v>2.32</v>
+      </c>
+      <c r="BN188">
+        <v>1.52</v>
+      </c>
+      <c r="BO188">
+        <v>3.05</v>
+      </c>
+      <c r="BP188">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7492346</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45668.45833333334</v>
+      </c>
+      <c r="F189">
+        <v>20</v>
+      </c>
+      <c r="G189" t="s">
+        <v>80</v>
+      </c>
+      <c r="H189" t="s">
+        <v>89</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>0</v>
+      </c>
+      <c r="O189" t="s">
+        <v>92</v>
+      </c>
+      <c r="P189" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q189">
+        <v>5</v>
+      </c>
+      <c r="R189">
+        <v>2.3</v>
+      </c>
+      <c r="S189">
+        <v>2.25</v>
+      </c>
+      <c r="T189">
+        <v>1.36</v>
+      </c>
+      <c r="U189">
+        <v>3</v>
+      </c>
+      <c r="V189">
+        <v>2.63</v>
+      </c>
+      <c r="W189">
+        <v>1.44</v>
+      </c>
+      <c r="X189">
+        <v>7</v>
+      </c>
+      <c r="Y189">
+        <v>1.1</v>
+      </c>
+      <c r="Z189">
+        <v>4.2</v>
+      </c>
+      <c r="AA189">
+        <v>4</v>
+      </c>
+      <c r="AB189">
+        <v>1.75</v>
+      </c>
+      <c r="AC189">
+        <v>1.04</v>
+      </c>
+      <c r="AD189">
+        <v>13</v>
+      </c>
+      <c r="AE189">
+        <v>1.26</v>
+      </c>
+      <c r="AF189">
+        <v>4</v>
+      </c>
+      <c r="AG189">
+        <v>1.62</v>
+      </c>
+      <c r="AH189">
+        <v>2.15</v>
+      </c>
+      <c r="AI189">
+        <v>1.8</v>
+      </c>
+      <c r="AJ189">
+        <v>1.95</v>
+      </c>
+      <c r="AK189">
+        <v>2.1</v>
+      </c>
+      <c r="AL189">
+        <v>1.25</v>
+      </c>
+      <c r="AM189">
+        <v>1.19</v>
+      </c>
+      <c r="AN189">
+        <v>1.44</v>
+      </c>
+      <c r="AO189">
+        <v>2</v>
+      </c>
+      <c r="AP189">
+        <v>1.4</v>
+      </c>
+      <c r="AQ189">
+        <v>1.91</v>
+      </c>
+      <c r="AR189">
+        <v>1.04</v>
+      </c>
+      <c r="AS189">
+        <v>1.7</v>
+      </c>
+      <c r="AT189">
+        <v>2.74</v>
+      </c>
+      <c r="AU189">
+        <v>4</v>
+      </c>
+      <c r="AV189">
+        <v>3</v>
+      </c>
+      <c r="AW189">
+        <v>9</v>
+      </c>
+      <c r="AX189">
+        <v>2</v>
+      </c>
+      <c r="AY189">
+        <v>16</v>
+      </c>
+      <c r="AZ189">
+        <v>6</v>
+      </c>
+      <c r="BA189">
+        <v>5</v>
+      </c>
+      <c r="BB189">
+        <v>3</v>
+      </c>
+      <c r="BC189">
+        <v>8</v>
+      </c>
+      <c r="BD189">
+        <v>3.15</v>
+      </c>
+      <c r="BE189">
+        <v>6.75</v>
+      </c>
+      <c r="BF189">
+        <v>1.44</v>
+      </c>
+      <c r="BG189">
+        <v>1.28</v>
+      </c>
+      <c r="BH189">
+        <v>3.2</v>
+      </c>
+      <c r="BI189">
+        <v>1.49</v>
+      </c>
+      <c r="BJ189">
+        <v>2.4</v>
+      </c>
+      <c r="BK189">
+        <v>1.78</v>
+      </c>
+      <c r="BL189">
+        <v>1.9</v>
+      </c>
+      <c r="BM189">
+        <v>2.2</v>
+      </c>
+      <c r="BN189">
+        <v>1.57</v>
+      </c>
+      <c r="BO189">
+        <v>2.85</v>
+      </c>
+      <c r="BP189">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -652,6 +652,9 @@
     <t>['34']</t>
   </si>
   <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -950,6 +953,9 @@
   </si>
   <si>
     <t>['6', '11', '90+1']</t>
+  </si>
+  <si>
+    <t>['55']</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP189"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1567,7 +1573,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2185,7 +2191,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2263,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ5">
         <v>1.2</v>
@@ -2391,7 +2397,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3009,7 +3015,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3215,7 +3221,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3627,7 +3633,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3833,7 +3839,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4245,7 +4251,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -5069,7 +5075,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5481,7 +5487,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5562,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR21">
         <v>1.14</v>
@@ -5687,7 +5693,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6099,7 +6105,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6386,7 +6392,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ25">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR25">
         <v>1.74</v>
@@ -6511,7 +6517,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6717,7 +6723,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6923,7 +6929,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7129,7 +7135,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7747,7 +7753,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8034,7 +8040,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ33">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR33">
         <v>0.96</v>
@@ -8237,7 +8243,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ34">
         <v>0.3</v>
@@ -8365,7 +8371,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8777,7 +8783,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8983,7 +8989,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9189,7 +9195,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9395,7 +9401,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9601,7 +9607,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9807,7 +9813,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10013,7 +10019,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10631,7 +10637,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10837,7 +10843,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11043,7 +11049,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11455,7 +11461,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11661,7 +11667,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11945,7 +11951,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ52">
         <v>0.7</v>
@@ -12073,7 +12079,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12279,7 +12285,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12360,7 +12366,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ54">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12485,7 +12491,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12691,7 +12697,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13103,7 +13109,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13721,7 +13727,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13802,7 +13808,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ61">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR61">
         <v>1.23</v>
@@ -14545,7 +14551,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14751,7 +14757,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14957,7 +14963,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15038,7 +15044,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ67">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR67">
         <v>1.09</v>
@@ -15369,7 +15375,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15575,7 +15581,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15781,7 +15787,7 @@
         <v>142</v>
       </c>
       <c r="P71" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16193,7 +16199,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16477,7 +16483,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ74">
         <v>1.2</v>
@@ -16811,7 +16817,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17017,7 +17023,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17223,7 +17229,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17429,7 +17435,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17635,7 +17641,7 @@
         <v>92</v>
       </c>
       <c r="P80" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17841,7 +17847,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18128,7 +18134,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ82">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18665,7 +18671,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19283,7 +19289,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19489,7 +19495,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19570,7 +19576,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ89">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -19695,7 +19701,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20107,7 +20113,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20313,7 +20319,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20391,7 +20397,7 @@
         <v>1.75</v>
       </c>
       <c r="AP93">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ93">
         <v>2.3</v>
@@ -20519,7 +20525,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20725,7 +20731,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20931,7 +20937,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21343,7 +21349,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21549,7 +21555,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22167,7 +22173,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22248,7 +22254,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ102">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR102">
         <v>1.16</v>
@@ -22579,7 +22585,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22785,7 +22791,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -22991,7 +22997,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23815,7 +23821,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -23896,7 +23902,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ110">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR110">
         <v>1.55</v>
@@ -24021,7 +24027,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24227,7 +24233,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24433,7 +24439,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24639,7 +24645,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25051,7 +25057,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25257,7 +25263,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25463,7 +25469,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26081,7 +26087,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26365,10 +26371,10 @@
         <v>2.2</v>
       </c>
       <c r="AP122">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ122">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26493,7 +26499,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26699,7 +26705,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26780,7 +26786,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ124">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -26905,7 +26911,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27111,7 +27117,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27729,7 +27735,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28631,7 +28637,7 @@
         <v>1.5</v>
       </c>
       <c r="AP133">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ133">
         <v>1.3</v>
@@ -28965,7 +28971,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29377,7 +29383,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29583,7 +29589,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29664,7 +29670,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ138">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR138">
         <v>1.39</v>
@@ -29789,7 +29795,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30613,7 +30619,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30819,7 +30825,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31106,7 +31112,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ145">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR145">
         <v>1.69</v>
@@ -31231,7 +31237,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31437,7 +31443,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31849,7 +31855,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32261,7 +32267,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32467,7 +32473,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32673,7 +32679,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32879,7 +32885,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33291,7 +33297,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33781,7 +33787,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ158">
         <v>1.56</v>
@@ -33909,7 +33915,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34115,7 +34121,7 @@
         <v>92</v>
       </c>
       <c r="P160" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q160">
         <v>5.5</v>
@@ -34321,7 +34327,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34527,7 +34533,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34733,7 +34739,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35145,7 +35151,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35226,7 +35232,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ165">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR165">
         <v>1.48</v>
@@ -35351,7 +35357,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35557,7 +35563,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35638,7 +35644,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ167">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -35763,7 +35769,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36381,7 +36387,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36587,7 +36593,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36793,7 +36799,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -36999,7 +37005,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37411,7 +37417,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37695,7 +37701,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ177">
         <v>0.5600000000000001</v>
@@ -38029,7 +38035,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38235,7 +38241,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38441,7 +38447,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38853,7 +38859,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -38934,7 +38940,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ183">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR183">
         <v>1.19</v>
@@ -39677,7 +39683,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39883,7 +39889,7 @@
         <v>163</v>
       </c>
       <c r="P188" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q188">
         <v>2.75</v>
@@ -40188,16 +40194,16 @@
         <v>3</v>
       </c>
       <c r="AW189">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY189">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ189">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA189">
         <v>5</v>
@@ -40246,6 +40252,418 @@
       </c>
       <c r="BP189">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7492345</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45668.58333333334</v>
+      </c>
+      <c r="F190">
+        <v>20</v>
+      </c>
+      <c r="G190" t="s">
+        <v>83</v>
+      </c>
+      <c r="H190" t="s">
+        <v>79</v>
+      </c>
+      <c r="I190">
+        <v>1</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>2</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>2</v>
+      </c>
+      <c r="O190" t="s">
+        <v>212</v>
+      </c>
+      <c r="P190" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q190">
+        <v>5.5</v>
+      </c>
+      <c r="R190">
+        <v>1.95</v>
+      </c>
+      <c r="S190">
+        <v>2.6</v>
+      </c>
+      <c r="T190">
+        <v>1.57</v>
+      </c>
+      <c r="U190">
+        <v>2.25</v>
+      </c>
+      <c r="V190">
+        <v>3.75</v>
+      </c>
+      <c r="W190">
+        <v>1.25</v>
+      </c>
+      <c r="X190">
+        <v>13</v>
+      </c>
+      <c r="Y190">
+        <v>1.04</v>
+      </c>
+      <c r="Z190">
+        <v>5</v>
+      </c>
+      <c r="AA190">
+        <v>3.25</v>
+      </c>
+      <c r="AB190">
+        <v>1.75</v>
+      </c>
+      <c r="AC190">
+        <v>1.12</v>
+      </c>
+      <c r="AD190">
+        <v>7</v>
+      </c>
+      <c r="AE190">
+        <v>1.53</v>
+      </c>
+      <c r="AF190">
+        <v>2.6</v>
+      </c>
+      <c r="AG190">
+        <v>2.2</v>
+      </c>
+      <c r="AH190">
+        <v>1.6</v>
+      </c>
+      <c r="AI190">
+        <v>2.2</v>
+      </c>
+      <c r="AJ190">
+        <v>1.62</v>
+      </c>
+      <c r="AK190">
+        <v>1.93</v>
+      </c>
+      <c r="AL190">
+        <v>1.33</v>
+      </c>
+      <c r="AM190">
+        <v>1.18</v>
+      </c>
+      <c r="AN190">
+        <v>1</v>
+      </c>
+      <c r="AO190">
+        <v>2</v>
+      </c>
+      <c r="AP190">
+        <v>1</v>
+      </c>
+      <c r="AQ190">
+        <v>1.89</v>
+      </c>
+      <c r="AR190">
+        <v>1.04</v>
+      </c>
+      <c r="AS190">
+        <v>1.24</v>
+      </c>
+      <c r="AT190">
+        <v>2.28</v>
+      </c>
+      <c r="AU190">
+        <v>3</v>
+      </c>
+      <c r="AV190">
+        <v>10</v>
+      </c>
+      <c r="AW190">
+        <v>9</v>
+      </c>
+      <c r="AX190">
+        <v>6</v>
+      </c>
+      <c r="AY190">
+        <v>15</v>
+      </c>
+      <c r="AZ190">
+        <v>20</v>
+      </c>
+      <c r="BA190">
+        <v>9</v>
+      </c>
+      <c r="BB190">
+        <v>1</v>
+      </c>
+      <c r="BC190">
+        <v>10</v>
+      </c>
+      <c r="BD190">
+        <v>2.3</v>
+      </c>
+      <c r="BE190">
+        <v>6.4</v>
+      </c>
+      <c r="BF190">
+        <v>1.76</v>
+      </c>
+      <c r="BG190">
+        <v>1.37</v>
+      </c>
+      <c r="BH190">
+        <v>2.8</v>
+      </c>
+      <c r="BI190">
+        <v>1.65</v>
+      </c>
+      <c r="BJ190">
+        <v>2.08</v>
+      </c>
+      <c r="BK190">
+        <v>2.04</v>
+      </c>
+      <c r="BL190">
+        <v>1.68</v>
+      </c>
+      <c r="BM190">
+        <v>2.63</v>
+      </c>
+      <c r="BN190">
+        <v>1.41</v>
+      </c>
+      <c r="BO190">
+        <v>3.45</v>
+      </c>
+      <c r="BP190">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7492342</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45668.69791666666</v>
+      </c>
+      <c r="F191">
+        <v>20</v>
+      </c>
+      <c r="G191" t="s">
+        <v>73</v>
+      </c>
+      <c r="H191" t="s">
+        <v>76</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>1</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>2</v>
+      </c>
+      <c r="O191" t="s">
+        <v>155</v>
+      </c>
+      <c r="P191" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q191">
+        <v>1.83</v>
+      </c>
+      <c r="R191">
+        <v>2.5</v>
+      </c>
+      <c r="S191">
+        <v>7.5</v>
+      </c>
+      <c r="T191">
+        <v>1.3</v>
+      </c>
+      <c r="U191">
+        <v>3.4</v>
+      </c>
+      <c r="V191">
+        <v>2.38</v>
+      </c>
+      <c r="W191">
+        <v>1.53</v>
+      </c>
+      <c r="X191">
+        <v>6</v>
+      </c>
+      <c r="Y191">
+        <v>1.13</v>
+      </c>
+      <c r="Z191">
+        <v>1.33</v>
+      </c>
+      <c r="AA191">
+        <v>4.75</v>
+      </c>
+      <c r="AB191">
+        <v>8</v>
+      </c>
+      <c r="AC191">
+        <v>1.02</v>
+      </c>
+      <c r="AD191">
+        <v>17</v>
+      </c>
+      <c r="AE191">
+        <v>1.19</v>
+      </c>
+      <c r="AF191">
+        <v>4.75</v>
+      </c>
+      <c r="AG191">
+        <v>1.87</v>
+      </c>
+      <c r="AH191">
+        <v>1.83</v>
+      </c>
+      <c r="AI191">
+        <v>1.95</v>
+      </c>
+      <c r="AJ191">
+        <v>1.8</v>
+      </c>
+      <c r="AK191">
+        <v>1.09</v>
+      </c>
+      <c r="AL191">
+        <v>1.17</v>
+      </c>
+      <c r="AM191">
+        <v>3</v>
+      </c>
+      <c r="AN191">
+        <v>1.78</v>
+      </c>
+      <c r="AO191">
+        <v>0.89</v>
+      </c>
+      <c r="AP191">
+        <v>1.7</v>
+      </c>
+      <c r="AQ191">
+        <v>0.9</v>
+      </c>
+      <c r="AR191">
+        <v>1.6</v>
+      </c>
+      <c r="AS191">
+        <v>1.12</v>
+      </c>
+      <c r="AT191">
+        <v>2.72</v>
+      </c>
+      <c r="AU191">
+        <v>12</v>
+      </c>
+      <c r="AV191">
+        <v>3</v>
+      </c>
+      <c r="AW191">
+        <v>13</v>
+      </c>
+      <c r="AX191">
+        <v>4</v>
+      </c>
+      <c r="AY191">
+        <v>28</v>
+      </c>
+      <c r="AZ191">
+        <v>9</v>
+      </c>
+      <c r="BA191">
+        <v>9</v>
+      </c>
+      <c r="BB191">
+        <v>1</v>
+      </c>
+      <c r="BC191">
+        <v>10</v>
+      </c>
+      <c r="BD191">
+        <v>1.27</v>
+      </c>
+      <c r="BE191">
+        <v>7.5</v>
+      </c>
+      <c r="BF191">
+        <v>4.1</v>
+      </c>
+      <c r="BG191">
+        <v>1.25</v>
+      </c>
+      <c r="BH191">
+        <v>3.45</v>
+      </c>
+      <c r="BI191">
+        <v>1.44</v>
+      </c>
+      <c r="BJ191">
+        <v>2.55</v>
+      </c>
+      <c r="BK191">
+        <v>1.71</v>
+      </c>
+      <c r="BL191">
+        <v>2</v>
+      </c>
+      <c r="BM191">
+        <v>2.1</v>
+      </c>
+      <c r="BN191">
+        <v>1.63</v>
+      </c>
+      <c r="BO191">
+        <v>2.65</v>
+      </c>
+      <c r="BP191">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1317,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ2">
         <v>2.5</v>
@@ -6598,7 +6598,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ26">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR26">
         <v>1.28</v>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -8449,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ35">
         <v>0.5600000000000001</v>
@@ -10718,7 +10718,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ46">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR46">
         <v>1.54</v>
@@ -12363,7 +12363,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ54">
         <v>1.89</v>
@@ -15250,7 +15250,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ68">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR68">
         <v>1.35</v>
@@ -16074,7 +16074,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ72">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR72">
         <v>1.87</v>
@@ -16277,7 +16277,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ73">
         <v>1.67</v>
@@ -21018,7 +21018,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ96">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR96">
         <v>1.44</v>
@@ -21427,7 +21427,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ98">
         <v>1.67</v>
@@ -24105,7 +24105,7 @@
         <v>0.57</v>
       </c>
       <c r="AP111">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ111">
         <v>0.64</v>
@@ -24520,7 +24520,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ113">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR113">
         <v>1.44</v>
@@ -26783,7 +26783,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ124">
         <v>0.9</v>
@@ -30082,7 +30082,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ140">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR140">
         <v>1.57</v>
@@ -30491,7 +30491,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ142">
         <v>1.2</v>
@@ -34611,7 +34611,7 @@
         <v>2.13</v>
       </c>
       <c r="AP162">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ162">
         <v>2.3</v>
@@ -35026,7 +35026,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ164">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR164">
         <v>1.54</v>
@@ -39352,7 +39352,7 @@
         <v>1</v>
       </c>
       <c r="AQ185">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR185">
         <v>1</v>
@@ -40664,6 +40664,212 @@
       </c>
       <c r="BP191">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7492340</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45669.35416666666</v>
+      </c>
+      <c r="F192">
+        <v>20</v>
+      </c>
+      <c r="G192" t="s">
+        <v>70</v>
+      </c>
+      <c r="H192" t="s">
+        <v>71</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
+        <v>162</v>
+      </c>
+      <c r="P192" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q192">
+        <v>2.5</v>
+      </c>
+      <c r="R192">
+        <v>2.2</v>
+      </c>
+      <c r="S192">
+        <v>4.33</v>
+      </c>
+      <c r="T192">
+        <v>1.36</v>
+      </c>
+      <c r="U192">
+        <v>3</v>
+      </c>
+      <c r="V192">
+        <v>2.75</v>
+      </c>
+      <c r="W192">
+        <v>1.4</v>
+      </c>
+      <c r="X192">
+        <v>7</v>
+      </c>
+      <c r="Y192">
+        <v>1.1</v>
+      </c>
+      <c r="Z192">
+        <v>2</v>
+      </c>
+      <c r="AA192">
+        <v>3.4</v>
+      </c>
+      <c r="AB192">
+        <v>3.6</v>
+      </c>
+      <c r="AC192">
+        <v>1.05</v>
+      </c>
+      <c r="AD192">
+        <v>11</v>
+      </c>
+      <c r="AE192">
+        <v>1.3</v>
+      </c>
+      <c r="AF192">
+        <v>3.6</v>
+      </c>
+      <c r="AG192">
+        <v>1.83</v>
+      </c>
+      <c r="AH192">
+        <v>1.95</v>
+      </c>
+      <c r="AI192">
+        <v>1.7</v>
+      </c>
+      <c r="AJ192">
+        <v>2.05</v>
+      </c>
+      <c r="AK192">
+        <v>1.26</v>
+      </c>
+      <c r="AL192">
+        <v>1.29</v>
+      </c>
+      <c r="AM192">
+        <v>1.8</v>
+      </c>
+      <c r="AN192">
+        <v>0.6</v>
+      </c>
+      <c r="AO192">
+        <v>0.89</v>
+      </c>
+      <c r="AP192">
+        <v>0.82</v>
+      </c>
+      <c r="AQ192">
+        <v>0.8</v>
+      </c>
+      <c r="AR192">
+        <v>1.24</v>
+      </c>
+      <c r="AS192">
+        <v>1.19</v>
+      </c>
+      <c r="AT192">
+        <v>2.43</v>
+      </c>
+      <c r="AU192">
+        <v>5</v>
+      </c>
+      <c r="AV192">
+        <v>4</v>
+      </c>
+      <c r="AW192">
+        <v>10</v>
+      </c>
+      <c r="AX192">
+        <v>6</v>
+      </c>
+      <c r="AY192">
+        <v>20</v>
+      </c>
+      <c r="AZ192">
+        <v>12</v>
+      </c>
+      <c r="BA192">
+        <v>6</v>
+      </c>
+      <c r="BB192">
+        <v>9</v>
+      </c>
+      <c r="BC192">
+        <v>15</v>
+      </c>
+      <c r="BD192">
+        <v>1.65</v>
+      </c>
+      <c r="BE192">
+        <v>6.5</v>
+      </c>
+      <c r="BF192">
+        <v>2.48</v>
+      </c>
+      <c r="BG192">
+        <v>1.3</v>
+      </c>
+      <c r="BH192">
+        <v>3.15</v>
+      </c>
+      <c r="BI192">
+        <v>1.52</v>
+      </c>
+      <c r="BJ192">
+        <v>2.33</v>
+      </c>
+      <c r="BK192">
+        <v>1.84</v>
+      </c>
+      <c r="BL192">
+        <v>1.84</v>
+      </c>
+      <c r="BM192">
+        <v>2.33</v>
+      </c>
+      <c r="BN192">
+        <v>1.52</v>
+      </c>
+      <c r="BO192">
+        <v>3.05</v>
+      </c>
+      <c r="BP192">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="317">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -655,6 +655,12 @@
     <t>['45+1']</t>
   </si>
   <si>
+    <t>['61', '65']</t>
+  </si>
+  <si>
+    <t>['5', '61']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -956,6 +962,9 @@
   </si>
   <si>
     <t>['55']</t>
+  </si>
+  <si>
+    <t>['58', '90+8']</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP192"/>
+  <dimension ref="A1:BP195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1573,7 +1582,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1654,7 +1663,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ2">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2191,7 +2200,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2397,7 +2406,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2475,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ6">
         <v>1.2</v>
@@ -2890,7 +2899,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ8">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3015,7 +3024,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3221,7 +3230,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3633,7 +3642,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3839,7 +3848,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4251,7 +4260,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -4947,7 +4956,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ18">
         <v>1.67</v>
@@ -5075,7 +5084,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5487,7 +5496,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5693,7 +5702,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5771,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ22">
         <v>1.2</v>
@@ -6105,7 +6114,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6183,7 +6192,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ24">
         <v>1.3</v>
@@ -6517,7 +6526,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6595,7 +6604,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ26">
         <v>0.8</v>
@@ -6723,7 +6732,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6929,7 +6938,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7010,7 +7019,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR28">
         <v>1.56</v>
@@ -7135,7 +7144,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7628,7 +7637,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ31">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR31">
         <v>1.66</v>
@@ -7753,7 +7762,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8371,7 +8380,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8452,7 +8461,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ35">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR35">
         <v>1.23</v>
@@ -8783,7 +8792,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8989,7 +8998,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9195,7 +9204,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9276,7 +9285,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ39">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR39">
         <v>1.18</v>
@@ -9401,7 +9410,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9607,7 +9616,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9688,7 +9697,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR41">
         <v>1.35</v>
@@ -9813,7 +9822,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10019,7 +10028,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10303,7 +10312,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ44">
         <v>1.56</v>
@@ -10637,7 +10646,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10843,7 +10852,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11049,7 +11058,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11461,7 +11470,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11667,7 +11676,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12079,7 +12088,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12160,7 +12169,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ53">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR53">
         <v>1.05</v>
@@ -12285,7 +12294,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12491,7 +12500,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12569,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ55">
         <v>1.91</v>
@@ -12697,7 +12706,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13109,7 +13118,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13190,7 +13199,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR58">
         <v>1.29</v>
@@ -13599,7 +13608,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ60">
         <v>0.78</v>
@@ -13727,7 +13736,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14011,7 +14020,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ62">
         <v>0.64</v>
@@ -14551,7 +14560,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14757,7 +14766,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14963,7 +14972,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15247,7 +15256,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ68">
         <v>0.8</v>
@@ -15375,7 +15384,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15581,7 +15590,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15662,7 +15671,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ70">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR70">
         <v>0.9399999999999999</v>
@@ -15787,7 +15796,7 @@
         <v>142</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16199,7 +16208,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16817,7 +16826,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17023,7 +17032,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17229,7 +17238,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17307,7 +17316,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ78">
         <v>1.91</v>
@@ -17435,7 +17444,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17641,7 +17650,7 @@
         <v>92</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17722,7 +17731,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ80">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR80">
         <v>2.02</v>
@@ -17847,7 +17856,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18543,7 +18552,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ84">
         <v>0.7</v>
@@ -18671,7 +18680,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -18752,7 +18761,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR85">
         <v>1.74</v>
@@ -19289,7 +19298,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19495,7 +19504,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19701,7 +19710,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19782,7 +19791,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ90">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR90">
         <v>1.56</v>
@@ -19988,7 +19997,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR91">
         <v>1.25</v>
@@ -20113,7 +20122,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20319,7 +20328,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20525,7 +20534,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20606,7 +20615,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ94">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR94">
         <v>0.91</v>
@@ -20731,7 +20740,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20809,7 +20818,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ95">
         <v>1.2</v>
@@ -20937,7 +20946,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21349,7 +21358,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21555,7 +21564,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22045,7 +22054,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ101">
         <v>0.7</v>
@@ -22173,7 +22182,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22585,7 +22594,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22663,7 +22672,7 @@
         <v>1.4</v>
       </c>
       <c r="AP104">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ104">
         <v>1.91</v>
@@ -22791,7 +22800,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -22997,7 +23006,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23078,7 +23087,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23821,7 +23830,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24027,7 +24036,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24233,7 +24242,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24439,7 +24448,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24517,7 +24526,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ113">
         <v>0.8</v>
@@ -24645,7 +24654,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25057,7 +25066,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25263,7 +25272,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25469,7 +25478,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25550,7 +25559,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR118">
         <v>1.7</v>
@@ -26087,7 +26096,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26168,7 +26177,7 @@
         <v>1</v>
       </c>
       <c r="AQ121">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26499,7 +26508,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26705,7 +26714,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26911,7 +26920,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27117,7 +27126,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27401,10 +27410,10 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ127">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27735,7 +27744,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28019,7 +28028,7 @@
         <v>0.17</v>
       </c>
       <c r="AP130">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ130">
         <v>0.7</v>
@@ -28228,7 +28237,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ131">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28843,7 +28852,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ134">
         <v>0.3</v>
@@ -28971,7 +28980,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29383,7 +29392,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29589,7 +29598,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29795,7 +29804,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30619,7 +30628,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30825,7 +30834,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31237,7 +31246,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31443,7 +31452,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31521,7 +31530,7 @@
         <v>0.63</v>
       </c>
       <c r="AP147">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ147">
         <v>0.64</v>
@@ -31727,7 +31736,7 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ148">
         <v>1.5</v>
@@ -31855,7 +31864,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32267,7 +32276,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32473,7 +32482,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32679,7 +32688,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32885,7 +32894,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33169,7 +33178,7 @@
         <v>2</v>
       </c>
       <c r="AP155">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ155">
         <v>1.67</v>
@@ -33297,7 +33306,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33378,7 +33387,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR156">
         <v>1.24</v>
@@ -33584,7 +33593,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ157">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR157">
         <v>1.44</v>
@@ -33915,7 +33924,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -33996,7 +34005,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ159">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR159">
         <v>1.56</v>
@@ -34121,7 +34130,7 @@
         <v>92</v>
       </c>
       <c r="P160" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q160">
         <v>5.5</v>
@@ -34327,7 +34336,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34533,7 +34542,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34739,7 +34748,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35151,7 +35160,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35229,7 +35238,7 @@
         <v>0.71</v>
       </c>
       <c r="AP165">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ165">
         <v>0.9</v>
@@ -35357,7 +35366,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35563,7 +35572,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35769,7 +35778,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36387,7 +36396,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36593,7 +36602,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36674,7 +36683,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ172">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR172">
         <v>1.46</v>
@@ -36799,7 +36808,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37005,7 +37014,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37289,7 +37298,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ175">
         <v>0.3</v>
@@ -37417,7 +37426,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37704,7 +37713,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ177">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR177">
         <v>1.56</v>
@@ -38035,7 +38044,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38113,10 +38122,10 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ179">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR179">
         <v>1.61</v>
@@ -38241,7 +38250,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38319,7 +38328,7 @@
         <v>1.33</v>
       </c>
       <c r="AP180">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ180">
         <v>1.3</v>
@@ -38447,7 +38456,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38859,7 +38868,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39683,7 +39692,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39889,7 +39898,7 @@
         <v>163</v>
       </c>
       <c r="P188" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q188">
         <v>2.75</v>
@@ -39988,16 +39997,16 @@
         <v>7</v>
       </c>
       <c r="AW188">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX188">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY188">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ188">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA188">
         <v>9</v>
@@ -40400,16 +40409,16 @@
         <v>10</v>
       </c>
       <c r="AW190">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX190">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY190">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ190">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA190">
         <v>9</v>
@@ -40507,7 +40516,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40606,16 +40615,16 @@
         <v>3</v>
       </c>
       <c r="AW191">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX191">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY191">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AZ191">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA191">
         <v>9</v>
@@ -40812,16 +40821,16 @@
         <v>4</v>
       </c>
       <c r="AW192">
+        <v>5</v>
+      </c>
+      <c r="AX192">
+        <v>3</v>
+      </c>
+      <c r="AY192">
+        <v>15</v>
+      </c>
+      <c r="AZ192">
         <v>10</v>
-      </c>
-      <c r="AX192">
-        <v>6</v>
-      </c>
-      <c r="AY192">
-        <v>20</v>
-      </c>
-      <c r="AZ192">
-        <v>12</v>
       </c>
       <c r="BA192">
         <v>6</v>
@@ -40870,6 +40879,624 @@
       </c>
       <c r="BP192">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7492347</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45669.45833333334</v>
+      </c>
+      <c r="F193">
+        <v>20</v>
+      </c>
+      <c r="G193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H193" t="s">
+        <v>81</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>1</v>
+      </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>1</v>
+      </c>
+      <c r="N193">
+        <v>1</v>
+      </c>
+      <c r="O193" t="s">
+        <v>92</v>
+      </c>
+      <c r="P193" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q193">
+        <v>8</v>
+      </c>
+      <c r="R193">
+        <v>2.6</v>
+      </c>
+      <c r="S193">
+        <v>1.73</v>
+      </c>
+      <c r="T193">
+        <v>1.29</v>
+      </c>
+      <c r="U193">
+        <v>3.5</v>
+      </c>
+      <c r="V193">
+        <v>2.25</v>
+      </c>
+      <c r="W193">
+        <v>1.57</v>
+      </c>
+      <c r="X193">
+        <v>5.5</v>
+      </c>
+      <c r="Y193">
+        <v>1.14</v>
+      </c>
+      <c r="Z193">
+        <v>10</v>
+      </c>
+      <c r="AA193">
+        <v>5.5</v>
+      </c>
+      <c r="AB193">
+        <v>1.28</v>
+      </c>
+      <c r="AC193">
+        <v>1.02</v>
+      </c>
+      <c r="AD193">
+        <v>21</v>
+      </c>
+      <c r="AE193">
+        <v>1.18</v>
+      </c>
+      <c r="AF193">
+        <v>5</v>
+      </c>
+      <c r="AG193">
+        <v>1.6</v>
+      </c>
+      <c r="AH193">
+        <v>2.3</v>
+      </c>
+      <c r="AI193">
+        <v>1.95</v>
+      </c>
+      <c r="AJ193">
+        <v>1.8</v>
+      </c>
+      <c r="AK193">
+        <v>3.5</v>
+      </c>
+      <c r="AL193">
+        <v>1.14</v>
+      </c>
+      <c r="AM193">
+        <v>1.06</v>
+      </c>
+      <c r="AN193">
+        <v>1.22</v>
+      </c>
+      <c r="AO193">
+        <v>2.5</v>
+      </c>
+      <c r="AP193">
+        <v>1.1</v>
+      </c>
+      <c r="AQ193">
+        <v>2.56</v>
+      </c>
+      <c r="AR193">
+        <v>1.41</v>
+      </c>
+      <c r="AS193">
+        <v>1.63</v>
+      </c>
+      <c r="AT193">
+        <v>3.04</v>
+      </c>
+      <c r="AU193">
+        <v>3</v>
+      </c>
+      <c r="AV193">
+        <v>7</v>
+      </c>
+      <c r="AW193">
+        <v>3</v>
+      </c>
+      <c r="AX193">
+        <v>6</v>
+      </c>
+      <c r="AY193">
+        <v>8</v>
+      </c>
+      <c r="AZ193">
+        <v>18</v>
+      </c>
+      <c r="BA193">
+        <v>4</v>
+      </c>
+      <c r="BB193">
+        <v>5</v>
+      </c>
+      <c r="BC193">
+        <v>9</v>
+      </c>
+      <c r="BD193">
+        <v>4.6</v>
+      </c>
+      <c r="BE193">
+        <v>8</v>
+      </c>
+      <c r="BF193">
+        <v>1.22</v>
+      </c>
+      <c r="BG193">
+        <v>1.28</v>
+      </c>
+      <c r="BH193">
+        <v>3.3</v>
+      </c>
+      <c r="BI193">
+        <v>1.49</v>
+      </c>
+      <c r="BJ193">
+        <v>2.4</v>
+      </c>
+      <c r="BK193">
+        <v>1.79</v>
+      </c>
+      <c r="BL193">
+        <v>1.9</v>
+      </c>
+      <c r="BM193">
+        <v>2.23</v>
+      </c>
+      <c r="BN193">
+        <v>1.56</v>
+      </c>
+      <c r="BO193">
+        <v>2.9</v>
+      </c>
+      <c r="BP193">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7492338</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45669.58333333334</v>
+      </c>
+      <c r="F194">
+        <v>20</v>
+      </c>
+      <c r="G194" t="s">
+        <v>74</v>
+      </c>
+      <c r="H194" t="s">
+        <v>86</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>2</v>
+      </c>
+      <c r="M194">
+        <v>2</v>
+      </c>
+      <c r="N194">
+        <v>4</v>
+      </c>
+      <c r="O194" t="s">
+        <v>213</v>
+      </c>
+      <c r="P194" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q194">
+        <v>3.6</v>
+      </c>
+      <c r="R194">
+        <v>2.05</v>
+      </c>
+      <c r="S194">
+        <v>3.25</v>
+      </c>
+      <c r="T194">
+        <v>1.44</v>
+      </c>
+      <c r="U194">
+        <v>2.63</v>
+      </c>
+      <c r="V194">
+        <v>3.25</v>
+      </c>
+      <c r="W194">
+        <v>1.33</v>
+      </c>
+      <c r="X194">
+        <v>10</v>
+      </c>
+      <c r="Y194">
+        <v>1.06</v>
+      </c>
+      <c r="Z194">
+        <v>2.62</v>
+      </c>
+      <c r="AA194">
+        <v>3.2</v>
+      </c>
+      <c r="AB194">
+        <v>2.62</v>
+      </c>
+      <c r="AC194">
+        <v>1.07</v>
+      </c>
+      <c r="AD194">
+        <v>9</v>
+      </c>
+      <c r="AE194">
+        <v>1.38</v>
+      </c>
+      <c r="AF194">
+        <v>3.1</v>
+      </c>
+      <c r="AG194">
+        <v>1.95</v>
+      </c>
+      <c r="AH194">
+        <v>1.75</v>
+      </c>
+      <c r="AI194">
+        <v>1.8</v>
+      </c>
+      <c r="AJ194">
+        <v>1.95</v>
+      </c>
+      <c r="AK194">
+        <v>1.47</v>
+      </c>
+      <c r="AL194">
+        <v>1.34</v>
+      </c>
+      <c r="AM194">
+        <v>1.43</v>
+      </c>
+      <c r="AN194">
+        <v>1.63</v>
+      </c>
+      <c r="AO194">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP194">
+        <v>1.56</v>
+      </c>
+      <c r="AQ194">
+        <v>0.6</v>
+      </c>
+      <c r="AR194">
+        <v>1.66</v>
+      </c>
+      <c r="AS194">
+        <v>1.2</v>
+      </c>
+      <c r="AT194">
+        <v>2.86</v>
+      </c>
+      <c r="AU194">
+        <v>9</v>
+      </c>
+      <c r="AV194">
+        <v>5</v>
+      </c>
+      <c r="AW194">
+        <v>6</v>
+      </c>
+      <c r="AX194">
+        <v>7</v>
+      </c>
+      <c r="AY194">
+        <v>17</v>
+      </c>
+      <c r="AZ194">
+        <v>15</v>
+      </c>
+      <c r="BA194">
+        <v>5</v>
+      </c>
+      <c r="BB194">
+        <v>4</v>
+      </c>
+      <c r="BC194">
+        <v>9</v>
+      </c>
+      <c r="BD194">
+        <v>1.95</v>
+      </c>
+      <c r="BE194">
+        <v>6.1</v>
+      </c>
+      <c r="BF194">
+        <v>2.05</v>
+      </c>
+      <c r="BG194">
+        <v>1.53</v>
+      </c>
+      <c r="BH194">
+        <v>2.3</v>
+      </c>
+      <c r="BI194">
+        <v>1.91</v>
+      </c>
+      <c r="BJ194">
+        <v>1.78</v>
+      </c>
+      <c r="BK194">
+        <v>2.48</v>
+      </c>
+      <c r="BL194">
+        <v>1.46</v>
+      </c>
+      <c r="BM194">
+        <v>3.3</v>
+      </c>
+      <c r="BN194">
+        <v>1.28</v>
+      </c>
+      <c r="BO194">
+        <v>4.4</v>
+      </c>
+      <c r="BP194">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7492344</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45669.69791666666</v>
+      </c>
+      <c r="F195">
+        <v>20</v>
+      </c>
+      <c r="G195" t="s">
+        <v>85</v>
+      </c>
+      <c r="H195" t="s">
+        <v>75</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>1</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>2</v>
+      </c>
+      <c r="O195" t="s">
+        <v>214</v>
+      </c>
+      <c r="P195" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q195">
+        <v>1.67</v>
+      </c>
+      <c r="R195">
+        <v>2.63</v>
+      </c>
+      <c r="S195">
+        <v>10</v>
+      </c>
+      <c r="T195">
+        <v>1.3</v>
+      </c>
+      <c r="U195">
+        <v>3.4</v>
+      </c>
+      <c r="V195">
+        <v>2.5</v>
+      </c>
+      <c r="W195">
+        <v>1.5</v>
+      </c>
+      <c r="X195">
+        <v>6</v>
+      </c>
+      <c r="Y195">
+        <v>1.13</v>
+      </c>
+      <c r="Z195">
+        <v>1.2</v>
+      </c>
+      <c r="AA195">
+        <v>6</v>
+      </c>
+      <c r="AB195">
+        <v>12</v>
+      </c>
+      <c r="AC195">
+        <v>1.02</v>
+      </c>
+      <c r="AD195">
+        <v>19</v>
+      </c>
+      <c r="AE195">
+        <v>1.19</v>
+      </c>
+      <c r="AF195">
+        <v>4.75</v>
+      </c>
+      <c r="AG195">
+        <v>1.61</v>
+      </c>
+      <c r="AH195">
+        <v>2.2</v>
+      </c>
+      <c r="AI195">
+        <v>2.2</v>
+      </c>
+      <c r="AJ195">
+        <v>1.62</v>
+      </c>
+      <c r="AK195">
+        <v>1.04</v>
+      </c>
+      <c r="AL195">
+        <v>1.13</v>
+      </c>
+      <c r="AM195">
+        <v>3.9</v>
+      </c>
+      <c r="AN195">
+        <v>2.33</v>
+      </c>
+      <c r="AO195">
+        <v>1</v>
+      </c>
+      <c r="AP195">
+        <v>2.4</v>
+      </c>
+      <c r="AQ195">
+        <v>0.9</v>
+      </c>
+      <c r="AR195">
+        <v>1.59</v>
+      </c>
+      <c r="AS195">
+        <v>0.97</v>
+      </c>
+      <c r="AT195">
+        <v>2.56</v>
+      </c>
+      <c r="AU195">
+        <v>4</v>
+      </c>
+      <c r="AV195">
+        <v>3</v>
+      </c>
+      <c r="AW195">
+        <v>11</v>
+      </c>
+      <c r="AX195">
+        <v>4</v>
+      </c>
+      <c r="AY195">
+        <v>19</v>
+      </c>
+      <c r="AZ195">
+        <v>9</v>
+      </c>
+      <c r="BA195">
+        <v>8</v>
+      </c>
+      <c r="BB195">
+        <v>1</v>
+      </c>
+      <c r="BC195">
+        <v>9</v>
+      </c>
+      <c r="BD195">
+        <v>1.16</v>
+      </c>
+      <c r="BE195">
+        <v>9.5</v>
+      </c>
+      <c r="BF195">
+        <v>5.4</v>
+      </c>
+      <c r="BG195">
+        <v>1.26</v>
+      </c>
+      <c r="BH195">
+        <v>3.4</v>
+      </c>
+      <c r="BI195">
+        <v>1.44</v>
+      </c>
+      <c r="BJ195">
+        <v>2.55</v>
+      </c>
+      <c r="BK195">
+        <v>1.72</v>
+      </c>
+      <c r="BL195">
+        <v>1.98</v>
+      </c>
+      <c r="BM195">
+        <v>2.12</v>
+      </c>
+      <c r="BN195">
+        <v>1.62</v>
+      </c>
+      <c r="BO195">
+        <v>2.65</v>
+      </c>
+      <c r="BP195">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -659,6 +659,9 @@
   </si>
   <si>
     <t>['5', '61']</t>
+  </si>
+  <si>
+    <t>['44', '63']</t>
   </si>
   <si>
     <t>['30', '82']</t>
@@ -1326,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP195"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1582,7 +1585,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1869,7 +1872,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ3">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2200,7 +2203,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2406,7 +2409,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3024,7 +3027,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3230,7 +3233,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3642,7 +3645,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3848,7 +3851,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4260,7 +4263,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -4338,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ15">
         <v>1.56</v>
@@ -5084,7 +5087,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5496,7 +5499,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5702,7 +5705,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6114,7 +6117,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6526,7 +6529,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6732,7 +6735,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6938,7 +6941,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7144,7 +7147,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7762,7 +7765,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8380,7 +8383,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8792,7 +8795,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8873,7 +8876,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ37">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR37">
         <v>0</v>
@@ -8998,7 +9001,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9204,7 +9207,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9282,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ39">
         <v>2.56</v>
@@ -9410,7 +9413,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9616,7 +9619,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9822,7 +9825,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10028,7 +10031,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10646,7 +10649,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10852,7 +10855,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11058,7 +11061,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11136,7 +11139,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ48">
         <v>1.67</v>
@@ -11470,7 +11473,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11676,7 +11679,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12088,7 +12091,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12294,7 +12297,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12500,7 +12503,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12706,7 +12709,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13118,7 +13121,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13405,7 +13408,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ59">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
         <v>0.91</v>
@@ -13736,7 +13739,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14560,7 +14563,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14766,7 +14769,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14972,7 +14975,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15384,7 +15387,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15590,7 +15593,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15668,7 +15671,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ70">
         <v>0.6</v>
@@ -15796,7 +15799,7 @@
         <v>142</v>
       </c>
       <c r="P71" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16208,7 +16211,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16826,7 +16829,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17032,7 +17035,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17113,7 +17116,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ77">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR77">
         <v>1.41</v>
@@ -17238,7 +17241,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17444,7 +17447,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17650,7 +17653,7 @@
         <v>92</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17856,7 +17859,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18680,7 +18683,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19298,7 +19301,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19376,7 +19379,7 @@
         <v>0.2</v>
       </c>
       <c r="AP88">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ88">
         <v>0.3</v>
@@ -19504,7 +19507,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19710,7 +19713,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20122,7 +20125,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20328,7 +20331,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20534,7 +20537,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20740,7 +20743,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20946,7 +20949,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21358,7 +21361,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21439,7 +21442,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ98">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR98">
         <v>1.23</v>
@@ -21564,7 +21567,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22182,7 +22185,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22466,7 +22469,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ103">
         <v>1.38</v>
@@ -22594,7 +22597,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22800,7 +22803,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -22881,7 +22884,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR105">
         <v>1.14</v>
@@ -23006,7 +23009,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23830,7 +23833,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24036,7 +24039,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24242,7 +24245,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24448,7 +24451,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24654,7 +24657,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25066,7 +25069,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25272,7 +25275,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25478,7 +25481,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25762,7 +25765,7 @@
         <v>1.2</v>
       </c>
       <c r="AP119">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ119">
         <v>1.5</v>
@@ -26096,7 +26099,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26508,7 +26511,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26714,7 +26717,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26920,7 +26923,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27001,7 +27004,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ125">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR125">
         <v>1.5</v>
@@ -27126,7 +27129,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27744,7 +27747,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28980,7 +28983,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29392,7 +29395,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29598,7 +29601,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29804,7 +29807,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30628,7 +30631,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30834,7 +30837,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31246,7 +31249,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31452,7 +31455,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31864,7 +31867,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -31942,7 +31945,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ149">
         <v>1.2</v>
@@ -32276,7 +32279,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32482,7 +32485,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32688,7 +32691,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32894,7 +32897,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33181,7 +33184,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ155">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR155">
         <v>1.61</v>
@@ -33306,7 +33309,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33924,7 +33927,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34130,7 +34133,7 @@
         <v>92</v>
       </c>
       <c r="P160" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q160">
         <v>5.5</v>
@@ -34336,7 +34339,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34542,7 +34545,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34748,7 +34751,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35160,7 +35163,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35366,7 +35369,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35572,7 +35575,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35650,7 +35653,7 @@
         <v>1.86</v>
       </c>
       <c r="AP167">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ167">
         <v>1.89</v>
@@ -35778,7 +35781,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36396,7 +36399,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36602,7 +36605,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36808,7 +36811,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37014,7 +37017,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37426,7 +37429,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37507,7 +37510,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ176">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR176">
         <v>1.42</v>
@@ -38044,7 +38047,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38250,7 +38253,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38456,7 +38459,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38868,7 +38871,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -38946,7 +38949,7 @@
         <v>0.63</v>
       </c>
       <c r="AP183">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AQ183">
         <v>0.9</v>
@@ -39692,7 +39695,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39898,7 +39901,7 @@
         <v>163</v>
       </c>
       <c r="P188" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q188">
         <v>2.75</v>
@@ -40516,7 +40519,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41134,7 +41137,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41497,6 +41500,212 @@
       </c>
       <c r="BP195">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7492343</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45670.69791666666</v>
+      </c>
+      <c r="F196">
+        <v>20</v>
+      </c>
+      <c r="G196" t="s">
+        <v>82</v>
+      </c>
+      <c r="H196" t="s">
+        <v>84</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>2</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>3</v>
+      </c>
+      <c r="O196" t="s">
+        <v>215</v>
+      </c>
+      <c r="P196" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q196">
+        <v>4.5</v>
+      </c>
+      <c r="R196">
+        <v>2.1</v>
+      </c>
+      <c r="S196">
+        <v>2.5</v>
+      </c>
+      <c r="T196">
+        <v>1.4</v>
+      </c>
+      <c r="U196">
+        <v>2.75</v>
+      </c>
+      <c r="V196">
+        <v>3</v>
+      </c>
+      <c r="W196">
+        <v>1.36</v>
+      </c>
+      <c r="X196">
+        <v>8</v>
+      </c>
+      <c r="Y196">
+        <v>1.08</v>
+      </c>
+      <c r="Z196">
+        <v>5.58</v>
+      </c>
+      <c r="AA196">
+        <v>3.93</v>
+      </c>
+      <c r="AB196">
+        <v>1.72</v>
+      </c>
+      <c r="AC196">
+        <v>1.05</v>
+      </c>
+      <c r="AD196">
+        <v>11</v>
+      </c>
+      <c r="AE196">
+        <v>1.33</v>
+      </c>
+      <c r="AF196">
+        <v>3.4</v>
+      </c>
+      <c r="AG196">
+        <v>2.1</v>
+      </c>
+      <c r="AH196">
+        <v>1.74</v>
+      </c>
+      <c r="AI196">
+        <v>1.8</v>
+      </c>
+      <c r="AJ196">
+        <v>1.95</v>
+      </c>
+      <c r="AK196">
+        <v>1.87</v>
+      </c>
+      <c r="AL196">
+        <v>1.29</v>
+      </c>
+      <c r="AM196">
+        <v>1.23</v>
+      </c>
+      <c r="AN196">
+        <v>0.3</v>
+      </c>
+      <c r="AO196">
+        <v>1.67</v>
+      </c>
+      <c r="AP196">
+        <v>0.55</v>
+      </c>
+      <c r="AQ196">
+        <v>1.5</v>
+      </c>
+      <c r="AR196">
+        <v>1.17</v>
+      </c>
+      <c r="AS196">
+        <v>1.25</v>
+      </c>
+      <c r="AT196">
+        <v>2.42</v>
+      </c>
+      <c r="AU196">
+        <v>4</v>
+      </c>
+      <c r="AV196">
+        <v>3</v>
+      </c>
+      <c r="AW196">
+        <v>7</v>
+      </c>
+      <c r="AX196">
+        <v>9</v>
+      </c>
+      <c r="AY196">
+        <v>13</v>
+      </c>
+      <c r="AZ196">
+        <v>16</v>
+      </c>
+      <c r="BA196">
+        <v>2</v>
+      </c>
+      <c r="BB196">
+        <v>4</v>
+      </c>
+      <c r="BC196">
+        <v>6</v>
+      </c>
+      <c r="BD196">
+        <v>2.7</v>
+      </c>
+      <c r="BE196">
+        <v>6.5</v>
+      </c>
+      <c r="BF196">
+        <v>1.55</v>
+      </c>
+      <c r="BG196">
+        <v>1.44</v>
+      </c>
+      <c r="BH196">
+        <v>2.55</v>
+      </c>
+      <c r="BI196">
+        <v>1.73</v>
+      </c>
+      <c r="BJ196">
+        <v>1.96</v>
+      </c>
+      <c r="BK196">
+        <v>2.18</v>
+      </c>
+      <c r="BL196">
+        <v>1.58</v>
+      </c>
+      <c r="BM196">
+        <v>2.8</v>
+      </c>
+      <c r="BN196">
+        <v>1.36</v>
+      </c>
+      <c r="BO196">
+        <v>3.8</v>
+      </c>
+      <c r="BP196">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="320">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,12 @@
     <t>['44', '63']</t>
   </si>
   <si>
+    <t>['60']</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -779,9 +785,6 @@
   </si>
   <si>
     <t>['61']</t>
-  </si>
-  <si>
-    <t>['60']</t>
   </si>
   <si>
     <t>['37', '56']</t>
@@ -968,6 +971,9 @@
   </si>
   <si>
     <t>['58', '90+8']</t>
+  </si>
+  <si>
+    <t>['71', '76']</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1591,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2203,7 +2209,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2409,7 +2415,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3027,7 +3033,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3233,7 +3239,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3645,7 +3651,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3851,7 +3857,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -3932,7 +3938,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ13">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR13">
         <v>1.45</v>
@@ -4263,7 +4269,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -5087,7 +5093,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5499,7 +5505,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5580,7 +5586,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR21">
         <v>1.14</v>
@@ -5705,7 +5711,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6117,7 +6123,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6529,7 +6535,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6735,7 +6741,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6816,7 +6822,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ27">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR27">
         <v>1.67</v>
@@ -6941,7 +6947,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7147,7 +7153,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7765,7 +7771,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7843,7 +7849,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
         <v>1.67</v>
@@ -8052,7 +8058,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ33">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR33">
         <v>0.96</v>
@@ -8383,7 +8389,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8795,7 +8801,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8873,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AQ37">
         <v>1.5</v>
@@ -9001,7 +9007,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9207,7 +9213,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9413,7 +9419,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9619,7 +9625,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9825,7 +9831,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10031,7 +10037,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10649,7 +10655,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10855,7 +10861,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11061,7 +11067,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11473,7 +11479,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11554,7 +11560,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ50">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11679,7 +11685,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11757,7 +11763,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AQ51">
         <v>0.64</v>
@@ -12091,7 +12097,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12297,7 +12303,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12378,7 +12384,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ54">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12503,7 +12509,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12709,7 +12715,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13121,7 +13127,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13199,7 +13205,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
         <v>0.9</v>
@@ -13739,7 +13745,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14563,7 +14569,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14641,7 +14647,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AQ65">
         <v>1.56</v>
@@ -14769,7 +14775,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14975,7 +14981,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15387,7 +15393,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15593,7 +15599,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15799,7 +15805,7 @@
         <v>142</v>
       </c>
       <c r="P71" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -15880,7 +15886,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ71">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR71">
         <v>1.68</v>
@@ -16083,7 +16089,7 @@
         <v>0.67</v>
       </c>
       <c r="AP72">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ72">
         <v>0.8</v>
@@ -16211,7 +16217,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16829,7 +16835,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17035,7 +17041,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17241,7 +17247,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17447,7 +17453,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17653,7 +17659,7 @@
         <v>92</v>
       </c>
       <c r="P80" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17859,7 +17865,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18683,7 +18689,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -18761,7 +18767,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AQ85">
         <v>0.9</v>
@@ -19301,7 +19307,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19507,7 +19513,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19588,7 +19594,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ89">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -19713,7 +19719,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20125,7 +20131,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20331,7 +20337,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20537,7 +20543,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20743,7 +20749,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20949,7 +20955,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21233,7 +21239,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AQ97">
         <v>0.78</v>
@@ -21361,7 +21367,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21567,7 +21573,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21645,7 +21651,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ99">
         <v>1.5</v>
@@ -22185,7 +22191,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22266,7 +22272,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ102">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR102">
         <v>1.16</v>
@@ -22472,7 +22478,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ103">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR103">
         <v>0.9399999999999999</v>
@@ -22597,7 +22603,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22803,7 +22809,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23009,7 +23015,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23833,7 +23839,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24039,7 +24045,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24245,7 +24251,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24451,7 +24457,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24657,7 +24663,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24738,7 +24744,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ114">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR114">
         <v>1.3</v>
@@ -25069,7 +25075,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25147,7 +25153,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AQ116">
         <v>1.2</v>
@@ -25275,7 +25281,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25481,7 +25487,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26099,7 +26105,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26386,7 +26392,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ122">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26511,7 +26517,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26717,7 +26723,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26923,7 +26929,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27001,7 +27007,7 @@
         <v>1.83</v>
       </c>
       <c r="AP125">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ125">
         <v>1.5</v>
@@ -27129,7 +27135,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27747,7 +27753,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28443,7 +28449,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ132">
         <v>0.78</v>
@@ -28983,7 +28989,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29395,7 +29401,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29601,7 +29607,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29682,7 +29688,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ138">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR138">
         <v>1.39</v>
@@ -29807,7 +29813,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30297,10 +30303,10 @@
         <v>1.33</v>
       </c>
       <c r="AP141">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AQ141">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR141">
         <v>1.73</v>
@@ -30631,7 +30637,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30837,7 +30843,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31249,7 +31255,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31455,7 +31461,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31867,7 +31873,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32279,7 +32285,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32485,7 +32491,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32691,7 +32697,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32897,7 +32903,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33309,7 +33315,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33593,7 +33599,7 @@
         <v>0.57</v>
       </c>
       <c r="AP157">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ157">
         <v>0.6</v>
@@ -33927,7 +33933,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34133,7 +34139,7 @@
         <v>92</v>
       </c>
       <c r="P160" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q160">
         <v>5.5</v>
@@ -34214,7 +34220,7 @@
         <v>1</v>
       </c>
       <c r="AQ160">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR160">
         <v>1.12</v>
@@ -34339,7 +34345,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34545,7 +34551,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34751,7 +34757,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35163,7 +35169,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35369,7 +35375,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35447,7 +35453,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AQ166">
         <v>1.3</v>
@@ -35575,7 +35581,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35656,7 +35662,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ167">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -35781,7 +35787,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36399,7 +36405,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36605,7 +36611,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36811,7 +36817,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37017,7 +37023,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37429,7 +37435,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37919,7 +37925,7 @@
         <v>0.5</v>
       </c>
       <c r="AP178">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ178">
         <v>0.7</v>
@@ -38047,7 +38053,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38253,7 +38259,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38459,7 +38465,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38871,7 +38877,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39695,7 +39701,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39901,7 +39907,7 @@
         <v>163</v>
       </c>
       <c r="P188" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q188">
         <v>2.75</v>
@@ -40394,7 +40400,7 @@
         <v>1</v>
       </c>
       <c r="AQ190">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR190">
         <v>1.04</v>
@@ -40519,7 +40525,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41137,7 +41143,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41706,6 +41712,418 @@
       </c>
       <c r="BP196">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7492329</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45671.60416666666</v>
+      </c>
+      <c r="F197">
+        <v>19</v>
+      </c>
+      <c r="G197" t="s">
+        <v>88</v>
+      </c>
+      <c r="H197" t="s">
+        <v>73</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>2</v>
+      </c>
+      <c r="N197">
+        <v>3</v>
+      </c>
+      <c r="O197" t="s">
+        <v>216</v>
+      </c>
+      <c r="P197" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q197">
+        <v>4.33</v>
+      </c>
+      <c r="R197">
+        <v>2.2</v>
+      </c>
+      <c r="S197">
+        <v>2.6</v>
+      </c>
+      <c r="T197">
+        <v>1.36</v>
+      </c>
+      <c r="U197">
+        <v>3</v>
+      </c>
+      <c r="V197">
+        <v>2.75</v>
+      </c>
+      <c r="W197">
+        <v>1.4</v>
+      </c>
+      <c r="X197">
+        <v>7</v>
+      </c>
+      <c r="Y197">
+        <v>1.1</v>
+      </c>
+      <c r="Z197">
+        <v>4</v>
+      </c>
+      <c r="AA197">
+        <v>3.5</v>
+      </c>
+      <c r="AB197">
+        <v>1.9</v>
+      </c>
+      <c r="AC197">
+        <v>1.05</v>
+      </c>
+      <c r="AD197">
+        <v>12</v>
+      </c>
+      <c r="AE197">
+        <v>1.28</v>
+      </c>
+      <c r="AF197">
+        <v>3.75</v>
+      </c>
+      <c r="AG197">
+        <v>1.85</v>
+      </c>
+      <c r="AH197">
+        <v>1.85</v>
+      </c>
+      <c r="AI197">
+        <v>1.7</v>
+      </c>
+      <c r="AJ197">
+        <v>2.05</v>
+      </c>
+      <c r="AK197">
+        <v>1.77</v>
+      </c>
+      <c r="AL197">
+        <v>1.28</v>
+      </c>
+      <c r="AM197">
+        <v>1.28</v>
+      </c>
+      <c r="AN197">
+        <v>1.5</v>
+      </c>
+      <c r="AO197">
+        <v>1.38</v>
+      </c>
+      <c r="AP197">
+        <v>1.33</v>
+      </c>
+      <c r="AQ197">
+        <v>1.56</v>
+      </c>
+      <c r="AR197">
+        <v>1.54</v>
+      </c>
+      <c r="AS197">
+        <v>1.46</v>
+      </c>
+      <c r="AT197">
+        <v>3</v>
+      </c>
+      <c r="AU197">
+        <v>5</v>
+      </c>
+      <c r="AV197">
+        <v>7</v>
+      </c>
+      <c r="AW197">
+        <v>6</v>
+      </c>
+      <c r="AX197">
+        <v>3</v>
+      </c>
+      <c r="AY197">
+        <v>13</v>
+      </c>
+      <c r="AZ197">
+        <v>13</v>
+      </c>
+      <c r="BA197">
+        <v>2</v>
+      </c>
+      <c r="BB197">
+        <v>4</v>
+      </c>
+      <c r="BC197">
+        <v>6</v>
+      </c>
+      <c r="BD197">
+        <v>2.5</v>
+      </c>
+      <c r="BE197">
+        <v>6.5</v>
+      </c>
+      <c r="BF197">
+        <v>1.65</v>
+      </c>
+      <c r="BG197">
+        <v>1.36</v>
+      </c>
+      <c r="BH197">
+        <v>2.8</v>
+      </c>
+      <c r="BI197">
+        <v>1.62</v>
+      </c>
+      <c r="BJ197">
+        <v>2.14</v>
+      </c>
+      <c r="BK197">
+        <v>2</v>
+      </c>
+      <c r="BL197">
+        <v>1.71</v>
+      </c>
+      <c r="BM197">
+        <v>2.55</v>
+      </c>
+      <c r="BN197">
+        <v>1.44</v>
+      </c>
+      <c r="BO197">
+        <v>3.4</v>
+      </c>
+      <c r="BP197">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7492328</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45671.69791666666</v>
+      </c>
+      <c r="F198">
+        <v>19</v>
+      </c>
+      <c r="G198" t="s">
+        <v>89</v>
+      </c>
+      <c r="H198" t="s">
+        <v>79</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>1</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>2</v>
+      </c>
+      <c r="O198" t="s">
+        <v>217</v>
+      </c>
+      <c r="P198" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q198">
+        <v>2.75</v>
+      </c>
+      <c r="R198">
+        <v>2.1</v>
+      </c>
+      <c r="S198">
+        <v>4.33</v>
+      </c>
+      <c r="T198">
+        <v>1.44</v>
+      </c>
+      <c r="U198">
+        <v>2.63</v>
+      </c>
+      <c r="V198">
+        <v>3</v>
+      </c>
+      <c r="W198">
+        <v>1.36</v>
+      </c>
+      <c r="X198">
+        <v>9</v>
+      </c>
+      <c r="Y198">
+        <v>1.07</v>
+      </c>
+      <c r="Z198">
+        <v>2.05</v>
+      </c>
+      <c r="AA198">
+        <v>3.3</v>
+      </c>
+      <c r="AB198">
+        <v>3.6</v>
+      </c>
+      <c r="AC198">
+        <v>1.06</v>
+      </c>
+      <c r="AD198">
+        <v>10</v>
+      </c>
+      <c r="AE198">
+        <v>1.33</v>
+      </c>
+      <c r="AF198">
+        <v>3.3</v>
+      </c>
+      <c r="AG198">
+        <v>1.95</v>
+      </c>
+      <c r="AH198">
+        <v>1.77</v>
+      </c>
+      <c r="AI198">
+        <v>1.8</v>
+      </c>
+      <c r="AJ198">
+        <v>1.95</v>
+      </c>
+      <c r="AK198">
+        <v>1.28</v>
+      </c>
+      <c r="AL198">
+        <v>1.3</v>
+      </c>
+      <c r="AM198">
+        <v>1.75</v>
+      </c>
+      <c r="AN198">
+        <v>2.63</v>
+      </c>
+      <c r="AO198">
+        <v>1.89</v>
+      </c>
+      <c r="AP198">
+        <v>2.44</v>
+      </c>
+      <c r="AQ198">
+        <v>1.8</v>
+      </c>
+      <c r="AR198">
+        <v>1.78</v>
+      </c>
+      <c r="AS198">
+        <v>1.29</v>
+      </c>
+      <c r="AT198">
+        <v>3.07</v>
+      </c>
+      <c r="AU198">
+        <v>7</v>
+      </c>
+      <c r="AV198">
+        <v>10</v>
+      </c>
+      <c r="AW198">
+        <v>7</v>
+      </c>
+      <c r="AX198">
+        <v>4</v>
+      </c>
+      <c r="AY198">
+        <v>18</v>
+      </c>
+      <c r="AZ198">
+        <v>18</v>
+      </c>
+      <c r="BA198">
+        <v>3</v>
+      </c>
+      <c r="BB198">
+        <v>3</v>
+      </c>
+      <c r="BC198">
+        <v>6</v>
+      </c>
+      <c r="BD198">
+        <v>1.47</v>
+      </c>
+      <c r="BE198">
+        <v>6.75</v>
+      </c>
+      <c r="BF198">
+        <v>2.95</v>
+      </c>
+      <c r="BG198">
+        <v>1.38</v>
+      </c>
+      <c r="BH198">
+        <v>2.75</v>
+      </c>
+      <c r="BI198">
+        <v>1.65</v>
+      </c>
+      <c r="BJ198">
+        <v>2.08</v>
+      </c>
+      <c r="BK198">
+        <v>2.04</v>
+      </c>
+      <c r="BL198">
+        <v>1.67</v>
+      </c>
+      <c r="BM198">
+        <v>2.65</v>
+      </c>
+      <c r="BN198">
+        <v>1.41</v>
+      </c>
+      <c r="BO198">
+        <v>3.45</v>
+      </c>
+      <c r="BP198">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="322">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,9 @@
     <t>['78']</t>
   </si>
   <si>
+    <t>['19', '45+1']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -974,6 +977,9 @@
   </si>
   <si>
     <t>['71', '76']</t>
+  </si>
+  <si>
+    <t>['15', '64']</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1591,7 +1597,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2209,7 +2215,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2415,7 +2421,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3033,7 +3039,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3239,7 +3245,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3651,7 +3657,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3857,7 +3863,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4141,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ14">
         <v>0.7</v>
@@ -4269,7 +4275,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -4968,7 +4974,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ18">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5093,7 +5099,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5505,7 +5511,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5711,7 +5717,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5995,7 +6001,7 @@
         <v>1.5</v>
       </c>
       <c r="AP23">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ23">
         <v>1.91</v>
@@ -6123,7 +6129,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6535,7 +6541,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6741,7 +6747,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6947,7 +6953,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7153,7 +7159,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7771,7 +7777,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7852,7 +7858,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR32">
         <v>0</v>
@@ -8389,7 +8395,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8801,7 +8807,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -9007,7 +9013,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9213,7 +9219,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9419,7 +9425,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9625,7 +9631,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9831,7 +9837,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10037,7 +10043,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10655,7 +10661,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10861,7 +10867,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11067,7 +11073,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11148,7 +11154,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ48">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR48">
         <v>0.9399999999999999</v>
@@ -11479,7 +11485,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11557,7 +11563,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ50">
         <v>1.56</v>
@@ -11685,7 +11691,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12097,7 +12103,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12303,7 +12309,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12509,7 +12515,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12715,7 +12721,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13127,7 +13133,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13745,7 +13751,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14569,7 +14575,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14775,7 +14781,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14853,7 +14859,7 @@
         <v>2.33</v>
       </c>
       <c r="AP66">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ66">
         <v>1.2</v>
@@ -14981,7 +14987,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15393,7 +15399,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15599,7 +15605,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16217,7 +16223,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16298,7 +16304,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ73">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR73">
         <v>1.29</v>
@@ -16835,7 +16841,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17041,7 +17047,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17247,7 +17253,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17453,7 +17459,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17865,7 +17871,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18689,7 +18695,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19307,7 +19313,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19513,7 +19519,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19591,7 +19597,7 @@
         <v>2.33</v>
       </c>
       <c r="AP89">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ89">
         <v>1.8</v>
@@ -19719,7 +19725,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20131,7 +20137,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20212,7 +20218,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ92">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR92">
         <v>1.35</v>
@@ -20337,7 +20343,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20543,7 +20549,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20749,7 +20755,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20955,7 +20961,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21367,7 +21373,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21573,7 +21579,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22191,7 +22197,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22603,7 +22609,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22809,7 +22815,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23015,7 +23021,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23299,7 +23305,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ107">
         <v>0.3</v>
@@ -23839,7 +23845,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24045,7 +24051,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24251,7 +24257,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24457,7 +24463,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24663,7 +24669,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25075,7 +25081,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25281,7 +25287,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25362,7 +25368,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ117">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR117">
         <v>1.63</v>
@@ -25487,7 +25493,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25977,7 +25983,7 @@
         <v>2</v>
       </c>
       <c r="AP120">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ120">
         <v>2.3</v>
@@ -26105,7 +26111,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26517,7 +26523,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26723,7 +26729,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26929,7 +26935,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27135,7 +27141,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27628,7 +27634,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ128">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR128">
         <v>1.58</v>
@@ -27753,7 +27759,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28989,7 +28995,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29401,7 +29407,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29607,7 +29613,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29813,7 +29819,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30097,7 +30103,7 @@
         <v>1.17</v>
       </c>
       <c r="AP140">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ140">
         <v>0.8</v>
@@ -30637,7 +30643,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30718,7 +30724,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ143">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR143">
         <v>1.47</v>
@@ -30843,7 +30849,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31255,7 +31261,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31461,7 +31467,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31873,7 +31879,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32285,7 +32291,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32491,7 +32497,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32697,7 +32703,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32903,7 +32909,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33315,7 +33321,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33933,7 +33939,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34139,7 +34145,7 @@
         <v>92</v>
       </c>
       <c r="P160" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q160">
         <v>5.5</v>
@@ -34345,7 +34351,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34426,7 +34432,7 @@
         <v>1</v>
       </c>
       <c r="AQ161">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR161">
         <v>1.07</v>
@@ -34551,7 +34557,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34757,7 +34763,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35169,7 +35175,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35375,7 +35381,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35581,7 +35587,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35787,7 +35793,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36071,7 +36077,7 @@
         <v>0.67</v>
       </c>
       <c r="AP169">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ169">
         <v>0.64</v>
@@ -36405,7 +36411,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36611,7 +36617,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36817,7 +36823,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37023,7 +37029,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37435,7 +37441,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38053,7 +38059,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38259,7 +38265,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38465,7 +38471,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38877,7 +38883,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39701,7 +39707,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39907,7 +39913,7 @@
         <v>163</v>
       </c>
       <c r="P188" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q188">
         <v>2.75</v>
@@ -40525,7 +40531,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41143,7 +41149,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41761,7 +41767,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42124,6 +42130,212 @@
       </c>
       <c r="BP198">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7492332</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45672.69791666666</v>
+      </c>
+      <c r="F199">
+        <v>19</v>
+      </c>
+      <c r="G199" t="s">
+        <v>81</v>
+      </c>
+      <c r="H199" t="s">
+        <v>74</v>
+      </c>
+      <c r="I199">
+        <v>2</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>3</v>
+      </c>
+      <c r="L199">
+        <v>2</v>
+      </c>
+      <c r="M199">
+        <v>2</v>
+      </c>
+      <c r="N199">
+        <v>4</v>
+      </c>
+      <c r="O199" t="s">
+        <v>218</v>
+      </c>
+      <c r="P199" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q199">
+        <v>1.95</v>
+      </c>
+      <c r="R199">
+        <v>2.38</v>
+      </c>
+      <c r="S199">
+        <v>6.5</v>
+      </c>
+      <c r="T199">
+        <v>1.33</v>
+      </c>
+      <c r="U199">
+        <v>3.25</v>
+      </c>
+      <c r="V199">
+        <v>2.63</v>
+      </c>
+      <c r="W199">
+        <v>1.44</v>
+      </c>
+      <c r="X199">
+        <v>6.5</v>
+      </c>
+      <c r="Y199">
+        <v>1.11</v>
+      </c>
+      <c r="Z199">
+        <v>1.37</v>
+      </c>
+      <c r="AA199">
+        <v>4.18</v>
+      </c>
+      <c r="AB199">
+        <v>6.47</v>
+      </c>
+      <c r="AC199">
+        <v>1.03</v>
+      </c>
+      <c r="AD199">
+        <v>13</v>
+      </c>
+      <c r="AE199">
+        <v>1.25</v>
+      </c>
+      <c r="AF199">
+        <v>4</v>
+      </c>
+      <c r="AG199">
+        <v>1.75</v>
+      </c>
+      <c r="AH199">
+        <v>2.05</v>
+      </c>
+      <c r="AI199">
+        <v>1.95</v>
+      </c>
+      <c r="AJ199">
+        <v>1.8</v>
+      </c>
+      <c r="AK199">
+        <v>1.11</v>
+      </c>
+      <c r="AL199">
+        <v>1.2</v>
+      </c>
+      <c r="AM199">
+        <v>2.65</v>
+      </c>
+      <c r="AN199">
+        <v>2.22</v>
+      </c>
+      <c r="AO199">
+        <v>1.67</v>
+      </c>
+      <c r="AP199">
+        <v>2.1</v>
+      </c>
+      <c r="AQ199">
+        <v>1.6</v>
+      </c>
+      <c r="AR199">
+        <v>1.57</v>
+      </c>
+      <c r="AS199">
+        <v>1.17</v>
+      </c>
+      <c r="AT199">
+        <v>2.74</v>
+      </c>
+      <c r="AU199">
+        <v>7</v>
+      </c>
+      <c r="AV199">
+        <v>7</v>
+      </c>
+      <c r="AW199">
+        <v>6</v>
+      </c>
+      <c r="AX199">
+        <v>8</v>
+      </c>
+      <c r="AY199">
+        <v>14</v>
+      </c>
+      <c r="AZ199">
+        <v>16</v>
+      </c>
+      <c r="BA199">
+        <v>3</v>
+      </c>
+      <c r="BB199">
+        <v>3</v>
+      </c>
+      <c r="BC199">
+        <v>6</v>
+      </c>
+      <c r="BD199">
+        <v>1.27</v>
+      </c>
+      <c r="BE199">
+        <v>7.5</v>
+      </c>
+      <c r="BF199">
+        <v>4.1</v>
+      </c>
+      <c r="BG199">
+        <v>1.35</v>
+      </c>
+      <c r="BH199">
+        <v>2.95</v>
+      </c>
+      <c r="BI199">
+        <v>1.63</v>
+      </c>
+      <c r="BJ199">
+        <v>2.1</v>
+      </c>
+      <c r="BK199">
+        <v>2.1</v>
+      </c>
+      <c r="BL199">
+        <v>1.63</v>
+      </c>
+      <c r="BM199">
+        <v>2.85</v>
+      </c>
+      <c r="BN199">
+        <v>1.36</v>
+      </c>
+      <c r="BO199">
+        <v>4.1</v>
+      </c>
+      <c r="BP199">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="328">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -673,6 +673,18 @@
     <t>['19', '45+1']</t>
   </si>
   <si>
+    <t>['25', '60', '73']</t>
+  </si>
+  <si>
+    <t>['22', '34', '69']</t>
+  </si>
+  <si>
+    <t>['59', '64']</t>
+  </si>
+  <si>
+    <t>['16', '55']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -980,6 +992,12 @@
   </si>
   <si>
     <t>['15', '64']</t>
+  </si>
+  <si>
+    <t>['4']</t>
+  </si>
+  <si>
+    <t>['27', '40', '78']</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1597,7 +1615,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2090,7 +2108,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ4">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2215,7 +2233,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2421,7 +2439,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2499,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ6">
         <v>1.2</v>
@@ -2708,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3039,7 +3057,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3245,7 +3263,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3529,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ11">
         <v>0.64</v>
@@ -3657,7 +3675,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3863,7 +3881,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -3944,7 +3962,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ13">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR13">
         <v>1.45</v>
@@ -4275,7 +4293,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -4356,7 +4374,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ15">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5099,7 +5117,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5177,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ19">
         <v>1.3</v>
@@ -5511,7 +5529,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5717,7 +5735,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6129,7 +6147,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6207,7 +6225,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ24">
         <v>1.3</v>
@@ -6541,7 +6559,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6747,7 +6765,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6828,7 +6846,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ27">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR27">
         <v>1.67</v>
@@ -6953,7 +6971,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7159,7 +7177,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7240,7 +7258,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ29">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR29">
         <v>1.74</v>
@@ -7649,7 +7667,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ31">
         <v>0.6</v>
@@ -7777,7 +7795,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8395,7 +8413,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8807,7 +8825,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8885,7 +8903,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ37">
         <v>1.5</v>
@@ -9013,7 +9031,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9094,7 +9112,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ38">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR38">
         <v>1.24</v>
@@ -9219,7 +9237,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9425,7 +9443,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9631,7 +9649,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9837,7 +9855,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10043,7 +10061,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10330,7 +10348,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ44">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10533,10 +10551,10 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ45">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR45">
         <v>1.23</v>
@@ -10661,7 +10679,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10867,7 +10885,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11073,7 +11091,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11357,7 +11375,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ49">
         <v>1.2</v>
@@ -11485,7 +11503,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11566,7 +11584,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ50">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11691,7 +11709,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11769,7 +11787,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ51">
         <v>0.64</v>
@@ -12103,7 +12121,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12309,7 +12327,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12515,7 +12533,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12593,7 +12611,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ55">
         <v>1.91</v>
@@ -12721,7 +12739,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13005,7 +13023,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ57">
         <v>0.3</v>
@@ -13133,7 +13151,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13626,7 +13644,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ60">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR60">
         <v>1.84</v>
@@ -13751,7 +13769,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14575,7 +14593,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14653,10 +14671,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ65">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14781,7 +14799,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14987,7 +15005,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15065,7 +15083,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67">
         <v>0.9</v>
@@ -15271,7 +15289,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ68">
         <v>0.8</v>
@@ -15399,7 +15417,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15605,7 +15623,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15892,7 +15910,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ71">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR71">
         <v>1.68</v>
@@ -16223,7 +16241,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16713,7 +16731,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ75">
         <v>1.5</v>
@@ -16841,7 +16859,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -16922,7 +16940,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ76">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR76">
         <v>0.85</v>
@@ -17047,7 +17065,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17253,7 +17271,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17459,7 +17477,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17743,7 +17761,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ80">
         <v>2.56</v>
@@ -17871,7 +17889,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -17952,7 +17970,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR81">
         <v>1.08</v>
@@ -18695,7 +18713,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -18773,7 +18791,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ85">
         <v>0.9</v>
@@ -19188,7 +19206,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ87">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR87">
         <v>1.49</v>
@@ -19313,7 +19331,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19519,7 +19537,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19725,7 +19743,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20137,7 +20155,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20343,7 +20361,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20424,7 +20442,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ93">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20549,7 +20567,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20755,7 +20773,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20961,7 +20979,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21039,7 +21057,7 @@
         <v>0.75</v>
       </c>
       <c r="AP96">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ96">
         <v>0.8</v>
@@ -21245,10 +21263,10 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ97">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR97">
         <v>1.88</v>
@@ -21373,7 +21391,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21579,7 +21597,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21863,7 +21881,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ100">
         <v>1.2</v>
@@ -22069,7 +22087,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ101">
         <v>0.7</v>
@@ -22197,7 +22215,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22484,7 +22502,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ103">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR103">
         <v>0.9399999999999999</v>
@@ -22609,7 +22627,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22815,7 +22833,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23021,7 +23039,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23514,7 +23532,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ108">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR108">
         <v>1.36</v>
@@ -23845,7 +23863,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24051,7 +24069,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24257,7 +24275,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24463,7 +24481,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24669,7 +24687,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24750,7 +24768,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ114">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR114">
         <v>1.3</v>
@@ -24953,7 +24971,7 @@
         <v>1.17</v>
       </c>
       <c r="AP115">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ115">
         <v>1.2</v>
@@ -25081,7 +25099,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25159,7 +25177,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ116">
         <v>1.2</v>
@@ -25287,7 +25305,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25365,7 +25383,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ117">
         <v>1.6</v>
@@ -25493,7 +25511,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25986,7 +26004,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ120">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR120">
         <v>1.62</v>
@@ -26111,7 +26129,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26523,7 +26541,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26729,7 +26747,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26935,7 +26953,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27141,7 +27159,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27222,7 +27240,7 @@
         <v>1</v>
       </c>
       <c r="AQ126">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR126">
         <v>1.11</v>
@@ -27759,7 +27777,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28458,7 +28476,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ132">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR132">
         <v>1.48</v>
@@ -28867,7 +28885,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ134">
         <v>0.3</v>
@@ -28995,7 +29013,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29076,7 +29094,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ135">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR135">
         <v>1.11</v>
@@ -29407,7 +29425,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29488,7 +29506,7 @@
         <v>1</v>
       </c>
       <c r="AQ137">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR137">
         <v>1.14</v>
@@ -29613,7 +29631,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29819,7 +29837,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29897,7 +29915,7 @@
         <v>1.86</v>
       </c>
       <c r="AP139">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ139">
         <v>1.91</v>
@@ -30309,10 +30327,10 @@
         <v>1.33</v>
       </c>
       <c r="AP141">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ141">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR141">
         <v>1.73</v>
@@ -30643,7 +30661,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30721,7 +30739,7 @@
         <v>1.57</v>
       </c>
       <c r="AP143">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ143">
         <v>1.6</v>
@@ -30849,7 +30867,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -30927,7 +30945,7 @@
         <v>0.57</v>
       </c>
       <c r="AP144">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ144">
         <v>0.7</v>
@@ -31261,7 +31279,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31467,7 +31485,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31879,7 +31897,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32291,7 +32309,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32497,7 +32515,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32578,7 +32596,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ152">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR152">
         <v>1.05</v>
@@ -32703,7 +32721,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32781,7 +32799,7 @@
         <v>0.25</v>
       </c>
       <c r="AP153">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ153">
         <v>0.3</v>
@@ -32909,7 +32927,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -32990,7 +33008,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ154">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR154">
         <v>1.38</v>
@@ -33193,7 +33211,7 @@
         <v>2</v>
       </c>
       <c r="AP155">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ155">
         <v>1.5</v>
@@ -33321,7 +33339,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33814,7 +33832,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ158">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR158">
         <v>1.52</v>
@@ -33939,7 +33957,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34145,7 +34163,7 @@
         <v>92</v>
       </c>
       <c r="P160" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q160">
         <v>5.5</v>
@@ -34226,7 +34244,7 @@
         <v>1</v>
       </c>
       <c r="AQ160">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR160">
         <v>1.12</v>
@@ -34351,7 +34369,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34557,7 +34575,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34638,7 +34656,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ162">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR162">
         <v>1.24</v>
@@ -34763,7 +34781,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35047,7 +35065,7 @@
         <v>1</v>
       </c>
       <c r="AP164">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ164">
         <v>0.8</v>
@@ -35175,7 +35193,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35381,7 +35399,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35459,7 +35477,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ166">
         <v>1.3</v>
@@ -35587,7 +35605,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35793,7 +35811,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36286,7 +36304,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ170">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR170">
         <v>1.34</v>
@@ -36411,7 +36429,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36492,7 +36510,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ171">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR171">
         <v>0.88</v>
@@ -36617,7 +36635,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36823,7 +36841,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37029,7 +37047,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37441,7 +37459,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37519,7 +37537,7 @@
         <v>1.75</v>
       </c>
       <c r="AP176">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ176">
         <v>1.5</v>
@@ -38059,7 +38077,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38137,7 +38155,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ179">
         <v>0.9</v>
@@ -38265,7 +38283,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38471,7 +38489,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38552,7 +38570,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ181">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR181">
         <v>1.57</v>
@@ -38883,7 +38901,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39170,7 +39188,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ184">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR184">
         <v>1.31</v>
@@ -39579,7 +39597,7 @@
         <v>1.67</v>
       </c>
       <c r="AP186">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ186">
         <v>1.5</v>
@@ -39707,7 +39725,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39913,7 +39931,7 @@
         <v>163</v>
       </c>
       <c r="P188" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q188">
         <v>2.75</v>
@@ -40531,7 +40549,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41149,7 +41167,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41227,7 +41245,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ194">
         <v>0.6</v>
@@ -41767,7 +41785,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -41848,7 +41866,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ197">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR197">
         <v>1.54</v>
@@ -42051,7 +42069,7 @@
         <v>1.89</v>
       </c>
       <c r="AP198">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ198">
         <v>1.8</v>
@@ -42179,7 +42197,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42336,6 +42354,830 @@
       </c>
       <c r="BP199">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7492357</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45674.69791666666</v>
+      </c>
+      <c r="F200">
+        <v>21</v>
+      </c>
+      <c r="G200" t="s">
+        <v>86</v>
+      </c>
+      <c r="H200" t="s">
+        <v>70</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>1</v>
+      </c>
+      <c r="K200">
+        <v>2</v>
+      </c>
+      <c r="L200">
+        <v>3</v>
+      </c>
+      <c r="M200">
+        <v>1</v>
+      </c>
+      <c r="N200">
+        <v>4</v>
+      </c>
+      <c r="O200" t="s">
+        <v>219</v>
+      </c>
+      <c r="P200" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q200">
+        <v>2.2</v>
+      </c>
+      <c r="R200">
+        <v>2.25</v>
+      </c>
+      <c r="S200">
+        <v>6</v>
+      </c>
+      <c r="T200">
+        <v>1.4</v>
+      </c>
+      <c r="U200">
+        <v>2.75</v>
+      </c>
+      <c r="V200">
+        <v>2.75</v>
+      </c>
+      <c r="W200">
+        <v>1.4</v>
+      </c>
+      <c r="X200">
+        <v>8</v>
+      </c>
+      <c r="Y200">
+        <v>1.08</v>
+      </c>
+      <c r="Z200">
+        <v>1.57</v>
+      </c>
+      <c r="AA200">
+        <v>4</v>
+      </c>
+      <c r="AB200">
+        <v>5.8</v>
+      </c>
+      <c r="AC200">
+        <v>1.05</v>
+      </c>
+      <c r="AD200">
+        <v>12</v>
+      </c>
+      <c r="AE200">
+        <v>1.3</v>
+      </c>
+      <c r="AF200">
+        <v>3.6</v>
+      </c>
+      <c r="AG200">
+        <v>1.93</v>
+      </c>
+      <c r="AH200">
+        <v>1.93</v>
+      </c>
+      <c r="AI200">
+        <v>1.95</v>
+      </c>
+      <c r="AJ200">
+        <v>1.8</v>
+      </c>
+      <c r="AK200">
+        <v>1.15</v>
+      </c>
+      <c r="AL200">
+        <v>1.24</v>
+      </c>
+      <c r="AM200">
+        <v>2.25</v>
+      </c>
+      <c r="AN200">
+        <v>1.8</v>
+      </c>
+      <c r="AO200">
+        <v>1.56</v>
+      </c>
+      <c r="AP200">
+        <v>1.91</v>
+      </c>
+      <c r="AQ200">
+        <v>1.4</v>
+      </c>
+      <c r="AR200">
+        <v>1.55</v>
+      </c>
+      <c r="AS200">
+        <v>0.97</v>
+      </c>
+      <c r="AT200">
+        <v>2.52</v>
+      </c>
+      <c r="AU200">
+        <v>8</v>
+      </c>
+      <c r="AV200">
+        <v>4</v>
+      </c>
+      <c r="AW200">
+        <v>9</v>
+      </c>
+      <c r="AX200">
+        <v>4</v>
+      </c>
+      <c r="AY200">
+        <v>19</v>
+      </c>
+      <c r="AZ200">
+        <v>9</v>
+      </c>
+      <c r="BA200">
+        <v>3</v>
+      </c>
+      <c r="BB200">
+        <v>2</v>
+      </c>
+      <c r="BC200">
+        <v>5</v>
+      </c>
+      <c r="BD200">
+        <v>1.35</v>
+      </c>
+      <c r="BE200">
+        <v>7</v>
+      </c>
+      <c r="BF200">
+        <v>3.55</v>
+      </c>
+      <c r="BG200">
+        <v>1.37</v>
+      </c>
+      <c r="BH200">
+        <v>2.8</v>
+      </c>
+      <c r="BI200">
+        <v>1.64</v>
+      </c>
+      <c r="BJ200">
+        <v>2.1</v>
+      </c>
+      <c r="BK200">
+        <v>2</v>
+      </c>
+      <c r="BL200">
+        <v>1.7</v>
+      </c>
+      <c r="BM200">
+        <v>2.55</v>
+      </c>
+      <c r="BN200">
+        <v>1.44</v>
+      </c>
+      <c r="BO200">
+        <v>3.4</v>
+      </c>
+      <c r="BP200">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7492349</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45675.45833333334</v>
+      </c>
+      <c r="F201">
+        <v>21</v>
+      </c>
+      <c r="G201" t="s">
+        <v>74</v>
+      </c>
+      <c r="H201" t="s">
+        <v>82</v>
+      </c>
+      <c r="I201">
+        <v>2</v>
+      </c>
+      <c r="J201">
+        <v>1</v>
+      </c>
+      <c r="K201">
+        <v>3</v>
+      </c>
+      <c r="L201">
+        <v>3</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201">
+        <v>4</v>
+      </c>
+      <c r="O201" t="s">
+        <v>220</v>
+      </c>
+      <c r="P201" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q201">
+        <v>2.25</v>
+      </c>
+      <c r="R201">
+        <v>2.2</v>
+      </c>
+      <c r="S201">
+        <v>5.5</v>
+      </c>
+      <c r="T201">
+        <v>1.44</v>
+      </c>
+      <c r="U201">
+        <v>2.63</v>
+      </c>
+      <c r="V201">
+        <v>3</v>
+      </c>
+      <c r="W201">
+        <v>1.36</v>
+      </c>
+      <c r="X201">
+        <v>9</v>
+      </c>
+      <c r="Y201">
+        <v>1.07</v>
+      </c>
+      <c r="Z201">
+        <v>1.6</v>
+      </c>
+      <c r="AA201">
+        <v>3.59</v>
+      </c>
+      <c r="AB201">
+        <v>5</v>
+      </c>
+      <c r="AC201">
+        <v>1.06</v>
+      </c>
+      <c r="AD201">
+        <v>10</v>
+      </c>
+      <c r="AE201">
+        <v>1.35</v>
+      </c>
+      <c r="AF201">
+        <v>3.25</v>
+      </c>
+      <c r="AG201">
+        <v>2.08</v>
+      </c>
+      <c r="AH201">
+        <v>1.8</v>
+      </c>
+      <c r="AI201">
+        <v>2</v>
+      </c>
+      <c r="AJ201">
+        <v>1.75</v>
+      </c>
+      <c r="AK201">
+        <v>1.15</v>
+      </c>
+      <c r="AL201">
+        <v>1.26</v>
+      </c>
+      <c r="AM201">
+        <v>2.2</v>
+      </c>
+      <c r="AN201">
+        <v>1.56</v>
+      </c>
+      <c r="AO201">
+        <v>0.78</v>
+      </c>
+      <c r="AP201">
+        <v>1.7</v>
+      </c>
+      <c r="AQ201">
+        <v>0.7</v>
+      </c>
+      <c r="AR201">
+        <v>1.71</v>
+      </c>
+      <c r="AS201">
+        <v>0.93</v>
+      </c>
+      <c r="AT201">
+        <v>2.64</v>
+      </c>
+      <c r="AU201">
+        <v>8</v>
+      </c>
+      <c r="AV201">
+        <v>2</v>
+      </c>
+      <c r="AW201">
+        <v>11</v>
+      </c>
+      <c r="AX201">
+        <v>2</v>
+      </c>
+      <c r="AY201">
+        <v>25</v>
+      </c>
+      <c r="AZ201">
+        <v>4</v>
+      </c>
+      <c r="BA201">
+        <v>4</v>
+      </c>
+      <c r="BB201">
+        <v>0</v>
+      </c>
+      <c r="BC201">
+        <v>4</v>
+      </c>
+      <c r="BD201">
+        <v>1.41</v>
+      </c>
+      <c r="BE201">
+        <v>6.75</v>
+      </c>
+      <c r="BF201">
+        <v>3.3</v>
+      </c>
+      <c r="BG201">
+        <v>1.41</v>
+      </c>
+      <c r="BH201">
+        <v>2.65</v>
+      </c>
+      <c r="BI201">
+        <v>1.68</v>
+      </c>
+      <c r="BJ201">
+        <v>2.04</v>
+      </c>
+      <c r="BK201">
+        <v>2.08</v>
+      </c>
+      <c r="BL201">
+        <v>1.65</v>
+      </c>
+      <c r="BM201">
+        <v>2.7</v>
+      </c>
+      <c r="BN201">
+        <v>1.4</v>
+      </c>
+      <c r="BO201">
+        <v>3.55</v>
+      </c>
+      <c r="BP201">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7492355</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45675.58333333334</v>
+      </c>
+      <c r="F202">
+        <v>21</v>
+      </c>
+      <c r="G202" t="s">
+        <v>79</v>
+      </c>
+      <c r="H202" t="s">
+        <v>73</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>2</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>2</v>
+      </c>
+      <c r="O202" t="s">
+        <v>221</v>
+      </c>
+      <c r="P202" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q202">
+        <v>2.88</v>
+      </c>
+      <c r="R202">
+        <v>2.05</v>
+      </c>
+      <c r="S202">
+        <v>4</v>
+      </c>
+      <c r="T202">
+        <v>1.5</v>
+      </c>
+      <c r="U202">
+        <v>2.5</v>
+      </c>
+      <c r="V202">
+        <v>3.4</v>
+      </c>
+      <c r="W202">
+        <v>1.3</v>
+      </c>
+      <c r="X202">
+        <v>10</v>
+      </c>
+      <c r="Y202">
+        <v>1.06</v>
+      </c>
+      <c r="Z202">
+        <v>2.2</v>
+      </c>
+      <c r="AA202">
+        <v>3.3</v>
+      </c>
+      <c r="AB202">
+        <v>3.4</v>
+      </c>
+      <c r="AC202">
+        <v>1.08</v>
+      </c>
+      <c r="AD202">
+        <v>9</v>
+      </c>
+      <c r="AE202">
+        <v>1.38</v>
+      </c>
+      <c r="AF202">
+        <v>3.1</v>
+      </c>
+      <c r="AG202">
+        <v>2.08</v>
+      </c>
+      <c r="AH202">
+        <v>1.71</v>
+      </c>
+      <c r="AI202">
+        <v>1.95</v>
+      </c>
+      <c r="AJ202">
+        <v>1.8</v>
+      </c>
+      <c r="AK202">
+        <v>1.32</v>
+      </c>
+      <c r="AL202">
+        <v>1.34</v>
+      </c>
+      <c r="AM202">
+        <v>1.61</v>
+      </c>
+      <c r="AN202">
+        <v>1.6</v>
+      </c>
+      <c r="AO202">
+        <v>1.56</v>
+      </c>
+      <c r="AP202">
+        <v>1.73</v>
+      </c>
+      <c r="AQ202">
+        <v>1.4</v>
+      </c>
+      <c r="AR202">
+        <v>1.44</v>
+      </c>
+      <c r="AS202">
+        <v>1.45</v>
+      </c>
+      <c r="AT202">
+        <v>2.89</v>
+      </c>
+      <c r="AU202">
+        <v>7</v>
+      </c>
+      <c r="AV202">
+        <v>4</v>
+      </c>
+      <c r="AW202">
+        <v>9</v>
+      </c>
+      <c r="AX202">
+        <v>10</v>
+      </c>
+      <c r="AY202">
+        <v>16</v>
+      </c>
+      <c r="AZ202">
+        <v>21</v>
+      </c>
+      <c r="BA202">
+        <v>5</v>
+      </c>
+      <c r="BB202">
+        <v>5</v>
+      </c>
+      <c r="BC202">
+        <v>10</v>
+      </c>
+      <c r="BD202">
+        <v>1.98</v>
+      </c>
+      <c r="BE202">
+        <v>6.25</v>
+      </c>
+      <c r="BF202">
+        <v>2.02</v>
+      </c>
+      <c r="BG202">
+        <v>1.34</v>
+      </c>
+      <c r="BH202">
+        <v>2.9</v>
+      </c>
+      <c r="BI202">
+        <v>1.58</v>
+      </c>
+      <c r="BJ202">
+        <v>2.18</v>
+      </c>
+      <c r="BK202">
+        <v>1.96</v>
+      </c>
+      <c r="BL202">
+        <v>1.73</v>
+      </c>
+      <c r="BM202">
+        <v>2.48</v>
+      </c>
+      <c r="BN202">
+        <v>1.46</v>
+      </c>
+      <c r="BO202">
+        <v>3.3</v>
+      </c>
+      <c r="BP202">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7492348</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45675.69791666666</v>
+      </c>
+      <c r="F203">
+        <v>21</v>
+      </c>
+      <c r="G203" t="s">
+        <v>89</v>
+      </c>
+      <c r="H203" t="s">
+        <v>85</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
+      <c r="J203">
+        <v>2</v>
+      </c>
+      <c r="K203">
+        <v>3</v>
+      </c>
+      <c r="L203">
+        <v>2</v>
+      </c>
+      <c r="M203">
+        <v>3</v>
+      </c>
+      <c r="N203">
+        <v>5</v>
+      </c>
+      <c r="O203" t="s">
+        <v>222</v>
+      </c>
+      <c r="P203" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q203">
+        <v>3</v>
+      </c>
+      <c r="R203">
+        <v>2.05</v>
+      </c>
+      <c r="S203">
+        <v>3.75</v>
+      </c>
+      <c r="T203">
+        <v>1.44</v>
+      </c>
+      <c r="U203">
+        <v>2.63</v>
+      </c>
+      <c r="V203">
+        <v>3.25</v>
+      </c>
+      <c r="W203">
+        <v>1.33</v>
+      </c>
+      <c r="X203">
+        <v>9</v>
+      </c>
+      <c r="Y203">
+        <v>1.07</v>
+      </c>
+      <c r="Z203">
+        <v>2.3</v>
+      </c>
+      <c r="AA203">
+        <v>3.25</v>
+      </c>
+      <c r="AB203">
+        <v>3.25</v>
+      </c>
+      <c r="AC203">
+        <v>1.07</v>
+      </c>
+      <c r="AD203">
+        <v>9.5</v>
+      </c>
+      <c r="AE203">
+        <v>1.36</v>
+      </c>
+      <c r="AF203">
+        <v>3.2</v>
+      </c>
+      <c r="AG203">
+        <v>1.95</v>
+      </c>
+      <c r="AH203">
+        <v>1.81</v>
+      </c>
+      <c r="AI203">
+        <v>1.91</v>
+      </c>
+      <c r="AJ203">
+        <v>1.91</v>
+      </c>
+      <c r="AK203">
+        <v>1.33</v>
+      </c>
+      <c r="AL203">
+        <v>1.33</v>
+      </c>
+      <c r="AM203">
+        <v>1.62</v>
+      </c>
+      <c r="AN203">
+        <v>2.44</v>
+      </c>
+      <c r="AO203">
+        <v>2.3</v>
+      </c>
+      <c r="AP203">
+        <v>2.2</v>
+      </c>
+      <c r="AQ203">
+        <v>2.36</v>
+      </c>
+      <c r="AR203">
+        <v>1.78</v>
+      </c>
+      <c r="AS203">
+        <v>1.22</v>
+      </c>
+      <c r="AT203">
+        <v>3</v>
+      </c>
+      <c r="AU203">
+        <v>7</v>
+      </c>
+      <c r="AV203">
+        <v>4</v>
+      </c>
+      <c r="AW203">
+        <v>9</v>
+      </c>
+      <c r="AX203">
+        <v>3</v>
+      </c>
+      <c r="AY203">
+        <v>19</v>
+      </c>
+      <c r="AZ203">
+        <v>8</v>
+      </c>
+      <c r="BA203">
+        <v>3</v>
+      </c>
+      <c r="BB203">
+        <v>1</v>
+      </c>
+      <c r="BC203">
+        <v>4</v>
+      </c>
+      <c r="BD203">
+        <v>1.65</v>
+      </c>
+      <c r="BE203">
+        <v>6.1</v>
+      </c>
+      <c r="BF203">
+        <v>2.55</v>
+      </c>
+      <c r="BG203">
+        <v>1.44</v>
+      </c>
+      <c r="BH203">
+        <v>2.55</v>
+      </c>
+      <c r="BI203">
+        <v>1.75</v>
+      </c>
+      <c r="BJ203">
+        <v>1.95</v>
+      </c>
+      <c r="BK203">
+        <v>2.18</v>
+      </c>
+      <c r="BL203">
+        <v>1.58</v>
+      </c>
+      <c r="BM203">
+        <v>2.8</v>
+      </c>
+      <c r="BN203">
+        <v>1.36</v>
+      </c>
+      <c r="BO203">
+        <v>3.8</v>
+      </c>
+      <c r="BP203">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="332">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,13 +676,25 @@
     <t>['25', '60', '73']</t>
   </si>
   <si>
-    <t>['22', '34', '69']</t>
+    <t>['23', '34', '69']</t>
   </si>
   <si>
     <t>['59', '64']</t>
   </si>
   <si>
     <t>['16', '55']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['60', '65', '80', '83']</t>
+  </si>
+  <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['55', '79', '89']</t>
   </si>
   <si>
     <t>['30', '82']</t>
@@ -934,9 +946,6 @@
     <t>['41', '45', '51', '53', '77', '90']</t>
   </si>
   <si>
-    <t>['56']</t>
-  </si>
-  <si>
     <t>['71', '80']</t>
   </si>
   <si>
@@ -998,6 +1007,9 @@
   </si>
   <si>
     <t>['27', '40', '78']</t>
+  </si>
+  <si>
+    <t>['2', '21', '58']</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP203"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1615,7 +1627,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1899,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ3">
         <v>1.5</v>
@@ -2233,7 +2245,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2314,7 +2326,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2439,7 +2451,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2723,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ7">
         <v>2.36</v>
@@ -2929,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ8">
         <v>0.6</v>
@@ -3057,7 +3069,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3138,7 +3150,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ9">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3263,7 +3275,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3675,7 +3687,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3756,7 +3768,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ12">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3881,7 +3893,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -3959,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ13">
         <v>1.4</v>
@@ -4165,10 +4177,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ14">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4293,7 +4305,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -4783,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ17">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5117,7 +5129,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5198,7 +5210,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ19">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5401,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ20">
         <v>0.64</v>
@@ -5529,7 +5541,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5607,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ21">
         <v>1.8</v>
@@ -5735,7 +5747,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5816,7 +5828,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6019,7 +6031,7 @@
         <v>1.5</v>
       </c>
       <c r="AP23">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ23">
         <v>1.91</v>
@@ -6147,7 +6159,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6228,7 +6240,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ24">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR24">
         <v>2.04</v>
@@ -6559,7 +6571,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6765,7 +6777,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6971,7 +6983,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7177,7 +7189,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7255,7 +7267,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ29">
         <v>0.7</v>
@@ -7795,7 +7807,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8288,7 +8300,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ34">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR34">
         <v>2.22</v>
@@ -8413,7 +8425,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8700,7 +8712,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR36">
         <v>1.46</v>
@@ -8825,7 +8837,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -9031,7 +9043,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9109,7 +9121,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ38">
         <v>2.36</v>
@@ -9237,7 +9249,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9443,7 +9455,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9521,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ40">
         <v>1.2</v>
@@ -9649,7 +9661,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9855,7 +9867,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9933,10 +9945,10 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ42">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR42">
         <v>1.4</v>
@@ -10061,7 +10073,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10139,10 +10151,10 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ43">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR43">
         <v>0.93</v>
@@ -10679,7 +10691,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10885,7 +10897,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -10963,10 +10975,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ47">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR47">
         <v>1.69</v>
@@ -11091,7 +11103,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11503,7 +11515,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11581,7 +11593,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ50">
         <v>1.4</v>
@@ -11709,7 +11721,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11996,7 +12008,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ52">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR52">
         <v>1.92</v>
@@ -12121,7 +12133,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12327,7 +12339,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12533,7 +12545,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12739,7 +12751,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -12820,7 +12832,7 @@
         <v>1</v>
       </c>
       <c r="AQ56">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR56">
         <v>1.02</v>
@@ -13026,7 +13038,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ57">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR57">
         <v>2.07</v>
@@ -13151,7 +13163,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13769,7 +13781,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13847,7 +13859,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ61">
         <v>0.9</v>
@@ -14259,10 +14271,10 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ63">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR63">
         <v>0.9</v>
@@ -14468,7 +14480,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ64">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR64">
         <v>1.02</v>
@@ -14593,7 +14605,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14799,7 +14811,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14877,10 +14889,10 @@
         <v>2.33</v>
       </c>
       <c r="AP66">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR66">
         <v>1.21</v>
@@ -15005,7 +15017,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15417,7 +15429,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15498,7 +15510,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ69">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15623,7 +15635,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15907,7 +15919,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ71">
         <v>1.4</v>
@@ -16241,7 +16253,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16734,7 +16746,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ75">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR75">
         <v>1.37</v>
@@ -16859,7 +16871,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17065,7 +17077,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17271,7 +17283,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17477,7 +17489,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17555,10 +17567,10 @@
         <v>1.75</v>
       </c>
       <c r="AP79">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ79">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR79">
         <v>1.44</v>
@@ -17889,7 +17901,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -17967,7 +17979,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ81">
         <v>0.7</v>
@@ -18588,7 +18600,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ84">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -18713,7 +18725,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -18997,10 +19009,10 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ86">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR86">
         <v>1.33</v>
@@ -19331,7 +19343,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19412,7 +19424,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ88">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR88">
         <v>0.85</v>
@@ -19537,7 +19549,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19615,7 +19627,7 @@
         <v>2.33</v>
       </c>
       <c r="AP89">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ89">
         <v>1.8</v>
@@ -19743,7 +19755,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19821,7 +19833,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ90">
         <v>0.6</v>
@@ -20155,7 +20167,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20233,7 +20245,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ92">
         <v>1.6</v>
@@ -20361,7 +20373,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20567,7 +20579,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20773,7 +20785,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20979,7 +20991,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21391,7 +21403,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21597,7 +21609,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21678,7 +21690,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ99">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR99">
         <v>1.62</v>
@@ -21884,7 +21896,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ100">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -22090,7 +22102,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ101">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22215,7 +22227,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22627,7 +22639,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22833,7 +22845,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23039,7 +23051,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23117,7 +23129,7 @@
         <v>0.8</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ106">
         <v>0.6</v>
@@ -23323,10 +23335,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ107">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -23529,7 +23541,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ108">
         <v>1.4</v>
@@ -23863,7 +23875,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24069,7 +24081,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24275,7 +24287,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24356,7 +24368,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ112">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR112">
         <v>1.28</v>
@@ -24481,7 +24493,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24687,7 +24699,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24765,7 +24777,7 @@
         <v>1.4</v>
       </c>
       <c r="AP114">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ114">
         <v>1.4</v>
@@ -24974,7 +24986,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ115">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR115">
         <v>1.54</v>
@@ -25099,7 +25111,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25305,7 +25317,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25511,7 +25523,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25589,7 +25601,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ118">
         <v>0.9</v>
@@ -25798,7 +25810,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ119">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR119">
         <v>0.96</v>
@@ -26001,7 +26013,7 @@
         <v>2</v>
       </c>
       <c r="AP120">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ120">
         <v>2.36</v>
@@ -26129,7 +26141,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26207,7 +26219,7 @@
         <v>2.2</v>
       </c>
       <c r="AP121">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ121">
         <v>2.56</v>
@@ -26541,7 +26553,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26619,7 +26631,7 @@
         <v>1.67</v>
       </c>
       <c r="AP123">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ123">
         <v>1.91</v>
@@ -26747,7 +26759,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26953,7 +26965,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27159,7 +27171,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27777,7 +27789,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28064,7 +28076,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ130">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR130">
         <v>1.48</v>
@@ -28267,7 +28279,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ131">
         <v>0.9</v>
@@ -28682,7 +28694,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ133">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR133">
         <v>1.55</v>
@@ -28888,7 +28900,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ134">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR134">
         <v>1.52</v>
@@ -29013,7 +29025,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29297,10 +29309,10 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ136">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR136">
         <v>1.24</v>
@@ -29425,7 +29437,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29631,7 +29643,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29837,7 +29849,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30121,7 +30133,7 @@
         <v>1.17</v>
       </c>
       <c r="AP140">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ140">
         <v>0.8</v>
@@ -30536,7 +30548,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ142">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR142">
         <v>1.3</v>
@@ -30661,7 +30673,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30867,7 +30879,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -30948,7 +30960,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ144">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31151,7 +31163,7 @@
         <v>0.83</v>
       </c>
       <c r="AP145">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ145">
         <v>0.9</v>
@@ -31279,7 +31291,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31357,10 +31369,10 @@
         <v>1.29</v>
       </c>
       <c r="AP146">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ146">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31485,7 +31497,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31772,7 +31784,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ148">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR148">
         <v>1.5</v>
@@ -31897,7 +31909,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32184,7 +32196,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ150">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR150">
         <v>0.84</v>
@@ -32309,7 +32321,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32387,7 +32399,7 @@
         <v>2</v>
       </c>
       <c r="AP151">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ151">
         <v>1.91</v>
@@ -32515,7 +32527,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32721,7 +32733,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32802,7 +32814,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ153">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -32927,7 +32939,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33339,7 +33351,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33417,7 +33429,7 @@
         <v>0.43</v>
       </c>
       <c r="AP156">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ156">
         <v>0.9</v>
@@ -33957,7 +33969,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34163,7 +34175,7 @@
         <v>92</v>
       </c>
       <c r="P160" t="s">
-        <v>306</v>
+        <v>225</v>
       </c>
       <c r="Q160">
         <v>5.5</v>
@@ -34241,7 +34253,7 @@
         <v>1.14</v>
       </c>
       <c r="AP160">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ160">
         <v>1.4</v>
@@ -34369,7 +34381,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34575,7 +34587,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34781,7 +34793,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34862,7 +34874,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ163">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR163">
         <v>1.36</v>
@@ -35193,7 +35205,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35399,7 +35411,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35480,7 +35492,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ166">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR166">
         <v>1.76</v>
@@ -35605,7 +35617,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35811,7 +35823,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -35889,7 +35901,7 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ168">
         <v>1.2</v>
@@ -36095,7 +36107,7 @@
         <v>0.67</v>
       </c>
       <c r="AP169">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ169">
         <v>0.64</v>
@@ -36301,7 +36313,7 @@
         <v>0.88</v>
       </c>
       <c r="AP170">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ170">
         <v>0.7</v>
@@ -36429,7 +36441,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36635,7 +36647,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36713,7 +36725,7 @@
         <v>2.43</v>
       </c>
       <c r="AP172">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ172">
         <v>2.56</v>
@@ -36841,7 +36853,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37047,7 +37059,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37128,7 +37140,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ174">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR174">
         <v>1.03</v>
@@ -37334,7 +37346,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ175">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR175">
         <v>1.48</v>
@@ -37459,7 +37471,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37952,7 +37964,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ178">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR178">
         <v>1.5</v>
@@ -38077,7 +38089,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38283,7 +38295,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38364,7 +38376,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ180">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR180">
         <v>1.47</v>
@@ -38489,7 +38501,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38567,7 +38579,7 @@
         <v>2.22</v>
       </c>
       <c r="AP181">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ181">
         <v>2.36</v>
@@ -38773,7 +38785,7 @@
         <v>1.22</v>
       </c>
       <c r="AP182">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ182">
         <v>1.2</v>
@@ -38901,7 +38913,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39600,7 +39612,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ186">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR186">
         <v>1.62</v>
@@ -39725,7 +39737,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39931,7 +39943,7 @@
         <v>163</v>
       </c>
       <c r="P188" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q188">
         <v>2.75</v>
@@ -40012,7 +40024,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ188">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR188">
         <v>0.97</v>
@@ -40549,7 +40561,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41167,7 +41179,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41785,7 +41797,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42197,7 +42209,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42275,7 +42287,7 @@
         <v>1.67</v>
       </c>
       <c r="AP199">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ199">
         <v>1.6</v>
@@ -42403,7 +42415,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42609,7 +42621,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43021,7 +43033,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43178,6 +43190,1036 @@
       </c>
       <c r="BP203">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7492352</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45676.35416666666</v>
+      </c>
+      <c r="F204">
+        <v>21</v>
+      </c>
+      <c r="G204" t="s">
+        <v>84</v>
+      </c>
+      <c r="H204" t="s">
+        <v>83</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>2</v>
+      </c>
+      <c r="O204" t="s">
+        <v>223</v>
+      </c>
+      <c r="P204" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q204">
+        <v>2.4</v>
+      </c>
+      <c r="R204">
+        <v>2.05</v>
+      </c>
+      <c r="S204">
+        <v>5.5</v>
+      </c>
+      <c r="T204">
+        <v>1.5</v>
+      </c>
+      <c r="U204">
+        <v>2.5</v>
+      </c>
+      <c r="V204">
+        <v>3.4</v>
+      </c>
+      <c r="W204">
+        <v>1.3</v>
+      </c>
+      <c r="X204">
+        <v>10</v>
+      </c>
+      <c r="Y204">
+        <v>1.06</v>
+      </c>
+      <c r="Z204">
+        <v>1.75</v>
+      </c>
+      <c r="AA204">
+        <v>3.4</v>
+      </c>
+      <c r="AB204">
+        <v>5.28</v>
+      </c>
+      <c r="AC204">
+        <v>1.07</v>
+      </c>
+      <c r="AD204">
+        <v>9.5</v>
+      </c>
+      <c r="AE204">
+        <v>1.4</v>
+      </c>
+      <c r="AF204">
+        <v>3</v>
+      </c>
+      <c r="AG204">
+        <v>2.16</v>
+      </c>
+      <c r="AH204">
+        <v>1.65</v>
+      </c>
+      <c r="AI204">
+        <v>2.05</v>
+      </c>
+      <c r="AJ204">
+        <v>1.7</v>
+      </c>
+      <c r="AK204">
+        <v>1.17</v>
+      </c>
+      <c r="AL204">
+        <v>1.28</v>
+      </c>
+      <c r="AM204">
+        <v>2.05</v>
+      </c>
+      <c r="AN204">
+        <v>1.89</v>
+      </c>
+      <c r="AO204">
+        <v>1.2</v>
+      </c>
+      <c r="AP204">
+        <v>1.8</v>
+      </c>
+      <c r="AQ204">
+        <v>1.18</v>
+      </c>
+      <c r="AR204">
+        <v>1.51</v>
+      </c>
+      <c r="AS204">
+        <v>1.13</v>
+      </c>
+      <c r="AT204">
+        <v>2.64</v>
+      </c>
+      <c r="AU204">
+        <v>7</v>
+      </c>
+      <c r="AV204">
+        <v>4</v>
+      </c>
+      <c r="AW204">
+        <v>14</v>
+      </c>
+      <c r="AX204">
+        <v>3</v>
+      </c>
+      <c r="AY204">
+        <v>29</v>
+      </c>
+      <c r="AZ204">
+        <v>8</v>
+      </c>
+      <c r="BA204">
+        <v>9</v>
+      </c>
+      <c r="BB204">
+        <v>2</v>
+      </c>
+      <c r="BC204">
+        <v>11</v>
+      </c>
+      <c r="BD204">
+        <v>1.26</v>
+      </c>
+      <c r="BE204">
+        <v>7</v>
+      </c>
+      <c r="BF204">
+        <v>4.35</v>
+      </c>
+      <c r="BG204">
+        <v>1.72</v>
+      </c>
+      <c r="BH204">
+        <v>1.98</v>
+      </c>
+      <c r="BI204">
+        <v>2.17</v>
+      </c>
+      <c r="BJ204">
+        <v>1.6</v>
+      </c>
+      <c r="BK204">
+        <v>2.8</v>
+      </c>
+      <c r="BL204">
+        <v>1.36</v>
+      </c>
+      <c r="BM204">
+        <v>3.9</v>
+      </c>
+      <c r="BN204">
+        <v>1.2</v>
+      </c>
+      <c r="BO204">
+        <v>5.3</v>
+      </c>
+      <c r="BP204">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7492350</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F205">
+        <v>21</v>
+      </c>
+      <c r="G205" t="s">
+        <v>76</v>
+      </c>
+      <c r="H205" t="s">
+        <v>78</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>1</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="L205">
+        <v>4</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>5</v>
+      </c>
+      <c r="O205" t="s">
+        <v>224</v>
+      </c>
+      <c r="P205" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q205">
+        <v>2.6</v>
+      </c>
+      <c r="R205">
+        <v>2.1</v>
+      </c>
+      <c r="S205">
+        <v>4.33</v>
+      </c>
+      <c r="T205">
+        <v>1.4</v>
+      </c>
+      <c r="U205">
+        <v>2.75</v>
+      </c>
+      <c r="V205">
+        <v>3</v>
+      </c>
+      <c r="W205">
+        <v>1.36</v>
+      </c>
+      <c r="X205">
+        <v>8</v>
+      </c>
+      <c r="Y205">
+        <v>1.08</v>
+      </c>
+      <c r="Z205">
+        <v>1.95</v>
+      </c>
+      <c r="AA205">
+        <v>3.4</v>
+      </c>
+      <c r="AB205">
+        <v>4.03</v>
+      </c>
+      <c r="AC205">
+        <v>1.06</v>
+      </c>
+      <c r="AD205">
+        <v>10</v>
+      </c>
+      <c r="AE205">
+        <v>1.32</v>
+      </c>
+      <c r="AF205">
+        <v>3.4</v>
+      </c>
+      <c r="AG205">
+        <v>1.95</v>
+      </c>
+      <c r="AH205">
+        <v>1.8</v>
+      </c>
+      <c r="AI205">
+        <v>1.8</v>
+      </c>
+      <c r="AJ205">
+        <v>1.95</v>
+      </c>
+      <c r="AK205">
+        <v>1.24</v>
+      </c>
+      <c r="AL205">
+        <v>1.3</v>
+      </c>
+      <c r="AM205">
+        <v>1.83</v>
+      </c>
+      <c r="AN205">
+        <v>0.9</v>
+      </c>
+      <c r="AO205">
+        <v>0.7</v>
+      </c>
+      <c r="AP205">
+        <v>1.09</v>
+      </c>
+      <c r="AQ205">
+        <v>0.64</v>
+      </c>
+      <c r="AR205">
+        <v>1.37</v>
+      </c>
+      <c r="AS205">
+        <v>1.15</v>
+      </c>
+      <c r="AT205">
+        <v>2.52</v>
+      </c>
+      <c r="AU205">
+        <v>8</v>
+      </c>
+      <c r="AV205">
+        <v>3</v>
+      </c>
+      <c r="AW205">
+        <v>12</v>
+      </c>
+      <c r="AX205">
+        <v>5</v>
+      </c>
+      <c r="AY205">
+        <v>24</v>
+      </c>
+      <c r="AZ205">
+        <v>9</v>
+      </c>
+      <c r="BA205">
+        <v>6</v>
+      </c>
+      <c r="BB205">
+        <v>1</v>
+      </c>
+      <c r="BC205">
+        <v>7</v>
+      </c>
+      <c r="BD205">
+        <v>1.5</v>
+      </c>
+      <c r="BE205">
+        <v>6.75</v>
+      </c>
+      <c r="BF205">
+        <v>2.9</v>
+      </c>
+      <c r="BG205">
+        <v>1.25</v>
+      </c>
+      <c r="BH205">
+        <v>3.45</v>
+      </c>
+      <c r="BI205">
+        <v>1.44</v>
+      </c>
+      <c r="BJ205">
+        <v>2.55</v>
+      </c>
+      <c r="BK205">
+        <v>1.72</v>
+      </c>
+      <c r="BL205">
+        <v>1.98</v>
+      </c>
+      <c r="BM205">
+        <v>2.14</v>
+      </c>
+      <c r="BN205">
+        <v>1.62</v>
+      </c>
+      <c r="BO205">
+        <v>2.7</v>
+      </c>
+      <c r="BP205">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7492356</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F206">
+        <v>21</v>
+      </c>
+      <c r="G206" t="s">
+        <v>71</v>
+      </c>
+      <c r="H206" t="s">
+        <v>87</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>1</v>
+      </c>
+      <c r="K206">
+        <v>1</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>1</v>
+      </c>
+      <c r="N206">
+        <v>2</v>
+      </c>
+      <c r="O206" t="s">
+        <v>225</v>
+      </c>
+      <c r="P206" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q206">
+        <v>2.75</v>
+      </c>
+      <c r="R206">
+        <v>2.25</v>
+      </c>
+      <c r="S206">
+        <v>3.75</v>
+      </c>
+      <c r="T206">
+        <v>1.33</v>
+      </c>
+      <c r="U206">
+        <v>3.25</v>
+      </c>
+      <c r="V206">
+        <v>2.63</v>
+      </c>
+      <c r="W206">
+        <v>1.44</v>
+      </c>
+      <c r="X206">
+        <v>6.5</v>
+      </c>
+      <c r="Y206">
+        <v>1.11</v>
+      </c>
+      <c r="Z206">
+        <v>2.15</v>
+      </c>
+      <c r="AA206">
+        <v>3.5</v>
+      </c>
+      <c r="AB206">
+        <v>3.29</v>
+      </c>
+      <c r="AC206">
+        <v>1.04</v>
+      </c>
+      <c r="AD206">
+        <v>13</v>
+      </c>
+      <c r="AE206">
+        <v>1.24</v>
+      </c>
+      <c r="AF206">
+        <v>4.2</v>
+      </c>
+      <c r="AG206">
+        <v>1.7</v>
+      </c>
+      <c r="AH206">
+        <v>2.08</v>
+      </c>
+      <c r="AI206">
+        <v>1.62</v>
+      </c>
+      <c r="AJ206">
+        <v>2.2</v>
+      </c>
+      <c r="AK206">
+        <v>1.34</v>
+      </c>
+      <c r="AL206">
+        <v>1.28</v>
+      </c>
+      <c r="AM206">
+        <v>1.68</v>
+      </c>
+      <c r="AN206">
+        <v>1.1</v>
+      </c>
+      <c r="AO206">
+        <v>0.3</v>
+      </c>
+      <c r="AP206">
+        <v>1.09</v>
+      </c>
+      <c r="AQ206">
+        <v>0.36</v>
+      </c>
+      <c r="AR206">
+        <v>1.29</v>
+      </c>
+      <c r="AS206">
+        <v>0.92</v>
+      </c>
+      <c r="AT206">
+        <v>2.21</v>
+      </c>
+      <c r="AU206">
+        <v>9</v>
+      </c>
+      <c r="AV206">
+        <v>3</v>
+      </c>
+      <c r="AW206">
+        <v>8</v>
+      </c>
+      <c r="AX206">
+        <v>2</v>
+      </c>
+      <c r="AY206">
+        <v>20</v>
+      </c>
+      <c r="AZ206">
+        <v>8</v>
+      </c>
+      <c r="BA206">
+        <v>8</v>
+      </c>
+      <c r="BB206">
+        <v>2</v>
+      </c>
+      <c r="BC206">
+        <v>10</v>
+      </c>
+      <c r="BD206">
+        <v>1.58</v>
+      </c>
+      <c r="BE206">
+        <v>6.75</v>
+      </c>
+      <c r="BF206">
+        <v>2.65</v>
+      </c>
+      <c r="BG206">
+        <v>1.26</v>
+      </c>
+      <c r="BH206">
+        <v>3.4</v>
+      </c>
+      <c r="BI206">
+        <v>1.47</v>
+      </c>
+      <c r="BJ206">
+        <v>2.48</v>
+      </c>
+      <c r="BK206">
+        <v>1.76</v>
+      </c>
+      <c r="BL206">
+        <v>1.94</v>
+      </c>
+      <c r="BM206">
+        <v>2.18</v>
+      </c>
+      <c r="BN206">
+        <v>1.58</v>
+      </c>
+      <c r="BO206">
+        <v>2.8</v>
+      </c>
+      <c r="BP206">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7492353</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45676.58333333334</v>
+      </c>
+      <c r="F207">
+        <v>21</v>
+      </c>
+      <c r="G207" t="s">
+        <v>75</v>
+      </c>
+      <c r="H207" t="s">
+        <v>77</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>2</v>
+      </c>
+      <c r="K207">
+        <v>2</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>3</v>
+      </c>
+      <c r="N207">
+        <v>3</v>
+      </c>
+      <c r="O207" t="s">
+        <v>92</v>
+      </c>
+      <c r="P207" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q207">
+        <v>5</v>
+      </c>
+      <c r="R207">
+        <v>2.2</v>
+      </c>
+      <c r="S207">
+        <v>2.38</v>
+      </c>
+      <c r="T207">
+        <v>1.4</v>
+      </c>
+      <c r="U207">
+        <v>2.75</v>
+      </c>
+      <c r="V207">
+        <v>3</v>
+      </c>
+      <c r="W207">
+        <v>1.36</v>
+      </c>
+      <c r="X207">
+        <v>8</v>
+      </c>
+      <c r="Y207">
+        <v>1.08</v>
+      </c>
+      <c r="Z207">
+        <v>4.4</v>
+      </c>
+      <c r="AA207">
+        <v>3.6</v>
+      </c>
+      <c r="AB207">
+        <v>1.75</v>
+      </c>
+      <c r="AC207">
+        <v>1.05</v>
+      </c>
+      <c r="AD207">
+        <v>12</v>
+      </c>
+      <c r="AE207">
+        <v>1.3</v>
+      </c>
+      <c r="AF207">
+        <v>3.6</v>
+      </c>
+      <c r="AG207">
+        <v>1.88</v>
+      </c>
+      <c r="AH207">
+        <v>1.92</v>
+      </c>
+      <c r="AI207">
+        <v>1.91</v>
+      </c>
+      <c r="AJ207">
+        <v>1.91</v>
+      </c>
+      <c r="AK207">
+        <v>2</v>
+      </c>
+      <c r="AL207">
+        <v>1.27</v>
+      </c>
+      <c r="AM207">
+        <v>1.2</v>
+      </c>
+      <c r="AN207">
+        <v>1</v>
+      </c>
+      <c r="AO207">
+        <v>1.5</v>
+      </c>
+      <c r="AP207">
+        <v>0.91</v>
+      </c>
+      <c r="AQ207">
+        <v>1.64</v>
+      </c>
+      <c r="AR207">
+        <v>1.12</v>
+      </c>
+      <c r="AS207">
+        <v>1.57</v>
+      </c>
+      <c r="AT207">
+        <v>2.69</v>
+      </c>
+      <c r="AU207">
+        <v>4</v>
+      </c>
+      <c r="AV207">
+        <v>6</v>
+      </c>
+      <c r="AW207">
+        <v>13</v>
+      </c>
+      <c r="AX207">
+        <v>9</v>
+      </c>
+      <c r="AY207">
+        <v>17</v>
+      </c>
+      <c r="AZ207">
+        <v>15</v>
+      </c>
+      <c r="BA207">
+        <v>5</v>
+      </c>
+      <c r="BB207">
+        <v>6</v>
+      </c>
+      <c r="BC207">
+        <v>11</v>
+      </c>
+      <c r="BD207">
+        <v>2.65</v>
+      </c>
+      <c r="BE207">
+        <v>6.75</v>
+      </c>
+      <c r="BF207">
+        <v>1.55</v>
+      </c>
+      <c r="BG207">
+        <v>1.26</v>
+      </c>
+      <c r="BH207">
+        <v>3.4</v>
+      </c>
+      <c r="BI207">
+        <v>1.46</v>
+      </c>
+      <c r="BJ207">
+        <v>2.5</v>
+      </c>
+      <c r="BK207">
+        <v>1.74</v>
+      </c>
+      <c r="BL207">
+        <v>1.95</v>
+      </c>
+      <c r="BM207">
+        <v>2.17</v>
+      </c>
+      <c r="BN207">
+        <v>1.6</v>
+      </c>
+      <c r="BO207">
+        <v>2.7</v>
+      </c>
+      <c r="BP207">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7492354</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45676.69791666666</v>
+      </c>
+      <c r="F208">
+        <v>21</v>
+      </c>
+      <c r="G208" t="s">
+        <v>81</v>
+      </c>
+      <c r="H208" t="s">
+        <v>72</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>3</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>4</v>
+      </c>
+      <c r="O208" t="s">
+        <v>226</v>
+      </c>
+      <c r="P208" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q208">
+        <v>1.62</v>
+      </c>
+      <c r="R208">
+        <v>2.75</v>
+      </c>
+      <c r="S208">
+        <v>10</v>
+      </c>
+      <c r="T208">
+        <v>1.29</v>
+      </c>
+      <c r="U208">
+        <v>3.5</v>
+      </c>
+      <c r="V208">
+        <v>2.25</v>
+      </c>
+      <c r="W208">
+        <v>1.57</v>
+      </c>
+      <c r="X208">
+        <v>5.5</v>
+      </c>
+      <c r="Y208">
+        <v>1.14</v>
+      </c>
+      <c r="Z208">
+        <v>1.22</v>
+      </c>
+      <c r="AA208">
+        <v>6</v>
+      </c>
+      <c r="AB208">
+        <v>11</v>
+      </c>
+      <c r="AC208">
+        <v>1.01</v>
+      </c>
+      <c r="AD208">
+        <v>23</v>
+      </c>
+      <c r="AE208">
+        <v>1.17</v>
+      </c>
+      <c r="AF208">
+        <v>5</v>
+      </c>
+      <c r="AG208">
+        <v>1.6</v>
+      </c>
+      <c r="AH208">
+        <v>2.3</v>
+      </c>
+      <c r="AI208">
+        <v>2.1</v>
+      </c>
+      <c r="AJ208">
+        <v>1.67</v>
+      </c>
+      <c r="AK208">
+        <v>1.04</v>
+      </c>
+      <c r="AL208">
+        <v>1.11</v>
+      </c>
+      <c r="AM208">
+        <v>4.1</v>
+      </c>
+      <c r="AN208">
+        <v>2.1</v>
+      </c>
+      <c r="AO208">
+        <v>1.3</v>
+      </c>
+      <c r="AP208">
+        <v>2.18</v>
+      </c>
+      <c r="AQ208">
+        <v>1.18</v>
+      </c>
+      <c r="AR208">
+        <v>1.57</v>
+      </c>
+      <c r="AS208">
+        <v>1.02</v>
+      </c>
+      <c r="AT208">
+        <v>2.59</v>
+      </c>
+      <c r="AU208">
+        <v>8</v>
+      </c>
+      <c r="AV208">
+        <v>2</v>
+      </c>
+      <c r="AW208">
+        <v>11</v>
+      </c>
+      <c r="AX208">
+        <v>4</v>
+      </c>
+      <c r="AY208">
+        <v>21</v>
+      </c>
+      <c r="AZ208">
+        <v>7</v>
+      </c>
+      <c r="BA208">
+        <v>7</v>
+      </c>
+      <c r="BB208">
+        <v>3</v>
+      </c>
+      <c r="BC208">
+        <v>10</v>
+      </c>
+      <c r="BD208">
+        <v>1.13</v>
+      </c>
+      <c r="BE208">
+        <v>10</v>
+      </c>
+      <c r="BF208">
+        <v>6.1</v>
+      </c>
+      <c r="BG208">
+        <v>1.2</v>
+      </c>
+      <c r="BH208">
+        <v>3.95</v>
+      </c>
+      <c r="BI208">
+        <v>1.35</v>
+      </c>
+      <c r="BJ208">
+        <v>2.9</v>
+      </c>
+      <c r="BK208">
+        <v>1.58</v>
+      </c>
+      <c r="BL208">
+        <v>2.2</v>
+      </c>
+      <c r="BM208">
+        <v>1.92</v>
+      </c>
+      <c r="BN208">
+        <v>1.77</v>
+      </c>
+      <c r="BO208">
+        <v>2.38</v>
+      </c>
+      <c r="BP208">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="334">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -697,6 +697,9 @@
     <t>['55', '79', '89']</t>
   </si>
   <si>
+    <t>['5', '44', '78', '90']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1010,6 +1013,9 @@
   </si>
   <si>
     <t>['2', '21', '58']</t>
+  </si>
+  <si>
+    <t>['84']</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1627,7 +1633,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2245,7 +2251,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2451,7 +2457,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2532,7 +2538,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ6">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3069,7 +3075,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3275,7 +3281,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3687,7 +3693,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3893,7 +3899,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4305,7 +4311,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -5129,7 +5135,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5541,7 +5547,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5747,7 +5753,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6159,7 +6165,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6571,7 +6577,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6777,7 +6783,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6983,7 +6989,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7189,7 +7195,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7807,7 +7813,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7885,7 +7891,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32">
         <v>1.6</v>
@@ -8425,7 +8431,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8837,7 +8843,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -9043,7 +9049,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9249,7 +9255,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9455,7 +9461,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9536,7 +9542,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ40">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -9661,7 +9667,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9867,7 +9873,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10073,7 +10079,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10691,7 +10697,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10897,7 +10903,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11103,7 +11109,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11390,7 +11396,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ49">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR49">
         <v>2.26</v>
@@ -11515,7 +11521,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11721,7 +11727,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12133,7 +12139,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12339,7 +12345,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12545,7 +12551,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12751,7 +12757,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13163,7 +13169,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13241,7 +13247,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
         <v>0.9</v>
@@ -13781,7 +13787,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14605,7 +14611,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14811,7 +14817,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15017,7 +15023,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15429,7 +15435,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15635,7 +15641,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16125,7 +16131,7 @@
         <v>0.67</v>
       </c>
       <c r="AP72">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
         <v>0.8</v>
@@ -16253,7 +16259,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16540,7 +16546,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ74">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR74">
         <v>1.89</v>
@@ -16871,7 +16877,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17077,7 +17083,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17283,7 +17289,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17489,7 +17495,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17901,7 +17907,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18725,7 +18731,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19343,7 +19349,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19549,7 +19555,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19755,7 +19761,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20167,7 +20173,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20373,7 +20379,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20579,7 +20585,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20785,7 +20791,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20866,7 +20872,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ95">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR95">
         <v>1.33</v>
@@ -20991,7 +20997,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21403,7 +21409,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21609,7 +21615,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21687,7 +21693,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ99">
         <v>1.64</v>
@@ -22227,7 +22233,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22639,7 +22645,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22845,7 +22851,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23051,7 +23057,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23875,7 +23881,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24081,7 +24087,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24287,7 +24293,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24493,7 +24499,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24699,7 +24705,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25111,7 +25117,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25192,7 +25198,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ116">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR116">
         <v>1.85</v>
@@ -25317,7 +25323,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25523,7 +25529,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26141,7 +26147,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26553,7 +26559,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26759,7 +26765,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26965,7 +26971,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27043,7 +27049,7 @@
         <v>1.83</v>
       </c>
       <c r="AP125">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125">
         <v>1.5</v>
@@ -27171,7 +27177,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27789,7 +27795,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -27870,7 +27876,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ129">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR129">
         <v>0.88</v>
@@ -28485,7 +28491,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ132">
         <v>0.7</v>
@@ -29025,7 +29031,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29437,7 +29443,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29643,7 +29649,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29849,7 +29855,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30673,7 +30679,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30879,7 +30885,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31291,7 +31297,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31497,7 +31503,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31909,7 +31915,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -31990,7 +31996,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ149">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR149">
         <v>1</v>
@@ -32321,7 +32327,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32527,7 +32533,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32733,7 +32739,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32939,7 +32945,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33351,7 +33357,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33635,7 +33641,7 @@
         <v>0.57</v>
       </c>
       <c r="AP157">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ157">
         <v>0.6</v>
@@ -33969,7 +33975,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34381,7 +34387,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34587,7 +34593,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34793,7 +34799,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35205,7 +35211,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35411,7 +35417,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35617,7 +35623,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35823,7 +35829,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -35904,7 +35910,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ168">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR168">
         <v>1.6</v>
@@ -36441,7 +36447,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36647,7 +36653,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36853,7 +36859,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37059,7 +37065,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37471,7 +37477,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37961,7 +37967,7 @@
         <v>0.5</v>
       </c>
       <c r="AP178">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ178">
         <v>0.64</v>
@@ -38089,7 +38095,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38295,7 +38301,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38501,7 +38507,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38788,7 +38794,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ182">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR182">
         <v>1.12</v>
@@ -38913,7 +38919,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39737,7 +39743,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39943,7 +39949,7 @@
         <v>163</v>
       </c>
       <c r="P188" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q188">
         <v>2.75</v>
@@ -40561,7 +40567,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41179,7 +41185,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41797,7 +41803,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -41875,7 +41881,7 @@
         <v>1.38</v>
       </c>
       <c r="AP197">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ197">
         <v>1.4</v>
@@ -42209,7 +42215,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42415,7 +42421,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42621,7 +42627,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43033,7 +43039,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43445,7 +43451,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43857,7 +43863,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44063,7 +44069,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>262</v>
+        <v>333</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44220,6 +44226,212 @@
       </c>
       <c r="BP208">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7492351</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45677.69791666666</v>
+      </c>
+      <c r="F209">
+        <v>21</v>
+      </c>
+      <c r="G209" t="s">
+        <v>88</v>
+      </c>
+      <c r="H209" t="s">
+        <v>80</v>
+      </c>
+      <c r="I209">
+        <v>2</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>2</v>
+      </c>
+      <c r="L209">
+        <v>4</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>5</v>
+      </c>
+      <c r="O209" t="s">
+        <v>227</v>
+      </c>
+      <c r="P209" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q209">
+        <v>2.75</v>
+      </c>
+      <c r="R209">
+        <v>2.1</v>
+      </c>
+      <c r="S209">
+        <v>4</v>
+      </c>
+      <c r="T209">
+        <v>1.44</v>
+      </c>
+      <c r="U209">
+        <v>2.63</v>
+      </c>
+      <c r="V209">
+        <v>3.25</v>
+      </c>
+      <c r="W209">
+        <v>1.33</v>
+      </c>
+      <c r="X209">
+        <v>9</v>
+      </c>
+      <c r="Y209">
+        <v>1.07</v>
+      </c>
+      <c r="Z209">
+        <v>2</v>
+      </c>
+      <c r="AA209">
+        <v>3.4</v>
+      </c>
+      <c r="AB209">
+        <v>3.6</v>
+      </c>
+      <c r="AC209">
+        <v>1.06</v>
+      </c>
+      <c r="AD209">
+        <v>10</v>
+      </c>
+      <c r="AE209">
+        <v>1.33</v>
+      </c>
+      <c r="AF209">
+        <v>3.3</v>
+      </c>
+      <c r="AG209">
+        <v>2</v>
+      </c>
+      <c r="AH209">
+        <v>1.8</v>
+      </c>
+      <c r="AI209">
+        <v>1.8</v>
+      </c>
+      <c r="AJ209">
+        <v>1.95</v>
+      </c>
+      <c r="AK209">
+        <v>1.28</v>
+      </c>
+      <c r="AL209">
+        <v>1.31</v>
+      </c>
+      <c r="AM209">
+        <v>1.73</v>
+      </c>
+      <c r="AN209">
+        <v>1.33</v>
+      </c>
+      <c r="AO209">
+        <v>1.2</v>
+      </c>
+      <c r="AP209">
+        <v>1.5</v>
+      </c>
+      <c r="AQ209">
+        <v>1.09</v>
+      </c>
+      <c r="AR209">
+        <v>1.52</v>
+      </c>
+      <c r="AS209">
+        <v>1.39</v>
+      </c>
+      <c r="AT209">
+        <v>2.91</v>
+      </c>
+      <c r="AU209">
+        <v>9</v>
+      </c>
+      <c r="AV209">
+        <v>3</v>
+      </c>
+      <c r="AW209">
+        <v>3</v>
+      </c>
+      <c r="AX209">
+        <v>4</v>
+      </c>
+      <c r="AY209">
+        <v>13</v>
+      </c>
+      <c r="AZ209">
+        <v>7</v>
+      </c>
+      <c r="BA209">
+        <v>3</v>
+      </c>
+      <c r="BB209">
+        <v>2</v>
+      </c>
+      <c r="BC209">
+        <v>5</v>
+      </c>
+      <c r="BD209">
+        <v>1.56</v>
+      </c>
+      <c r="BE209">
+        <v>6.75</v>
+      </c>
+      <c r="BF209">
+        <v>2.65</v>
+      </c>
+      <c r="BG209">
+        <v>1.3</v>
+      </c>
+      <c r="BH209">
+        <v>3.05</v>
+      </c>
+      <c r="BI209">
+        <v>1.54</v>
+      </c>
+      <c r="BJ209">
+        <v>2.3</v>
+      </c>
+      <c r="BK209">
+        <v>1.88</v>
+      </c>
+      <c r="BL209">
+        <v>1.81</v>
+      </c>
+      <c r="BM209">
+        <v>2.33</v>
+      </c>
+      <c r="BN209">
+        <v>1.5</v>
+      </c>
+      <c r="BO209">
+        <v>3.05</v>
+      </c>
+      <c r="BP209">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="335">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -700,6 +700,9 @@
     <t>['5', '44', '78', '90']</t>
   </si>
   <si>
+    <t>['6', '61']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1377,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1633,7 +1636,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2251,7 +2254,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2457,7 +2460,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3075,7 +3078,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3281,7 +3284,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3693,7 +3696,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3899,7 +3902,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4311,7 +4314,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -4595,7 +4598,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ16">
         <v>1.91</v>
@@ -5135,7 +5138,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5547,7 +5550,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5753,7 +5756,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6165,7 +6168,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6452,7 +6455,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ25">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR25">
         <v>1.74</v>
@@ -6577,7 +6580,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6783,7 +6786,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6989,7 +6992,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7195,7 +7198,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7813,7 +7816,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8431,7 +8434,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8715,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ36">
         <v>0.64</v>
@@ -8843,7 +8846,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -9049,7 +9052,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9255,7 +9258,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9461,7 +9464,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9667,7 +9670,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9873,7 +9876,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10079,7 +10082,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10697,7 +10700,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10903,7 +10906,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11109,7 +11112,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11521,7 +11524,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11727,7 +11730,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12139,7 +12142,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12345,7 +12348,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12551,7 +12554,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12757,7 +12760,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -12835,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ56">
         <v>1.64</v>
@@ -13169,7 +13172,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13787,7 +13790,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13868,7 +13871,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ61">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR61">
         <v>1.23</v>
@@ -14611,7 +14614,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14817,7 +14820,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15023,7 +15026,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15104,7 +15107,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ67">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR67">
         <v>1.09</v>
@@ -15435,7 +15438,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15641,7 +15644,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16259,7 +16262,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16877,7 +16880,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17083,7 +17086,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17289,7 +17292,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17495,7 +17498,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17907,7 +17910,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18194,7 +18197,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ82">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18397,7 +18400,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ83">
         <v>0.64</v>
@@ -18731,7 +18734,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19349,7 +19352,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19555,7 +19558,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19761,7 +19764,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20173,7 +20176,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20379,7 +20382,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20585,7 +20588,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20791,7 +20794,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20997,7 +21000,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21409,7 +21412,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21615,7 +21618,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22233,7 +22236,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22645,7 +22648,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22851,7 +22854,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -22929,7 +22932,7 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ105">
         <v>1.5</v>
@@ -23057,7 +23060,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23881,7 +23884,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -23962,7 +23965,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ110">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR110">
         <v>1.55</v>
@@ -24087,7 +24090,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24293,7 +24296,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24499,7 +24502,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24705,7 +24708,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25117,7 +25120,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25323,7 +25326,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25529,7 +25532,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26147,7 +26150,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26559,7 +26562,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26765,7 +26768,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26846,7 +26849,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ124">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -26971,7 +26974,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27177,7 +27180,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27255,7 +27258,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ126">
         <v>0.7</v>
@@ -27795,7 +27798,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29031,7 +29034,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29443,7 +29446,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29521,7 +29524,7 @@
         <v>1.83</v>
       </c>
       <c r="AP137">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
         <v>2.36</v>
@@ -29649,7 +29652,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29855,7 +29858,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30679,7 +30682,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30885,7 +30888,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31172,7 +31175,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ145">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR145">
         <v>1.69</v>
@@ -31297,7 +31300,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31503,7 +31506,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31915,7 +31918,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32327,7 +32330,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32533,7 +32536,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32739,7 +32742,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32945,7 +32948,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33357,7 +33360,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33975,7 +33978,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34387,7 +34390,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34465,7 +34468,7 @@
         <v>1.5</v>
       </c>
       <c r="AP161">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ161">
         <v>1.6</v>
@@ -34593,7 +34596,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34799,7 +34802,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35211,7 +35214,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35292,7 +35295,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ165">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR165">
         <v>1.48</v>
@@ -35417,7 +35420,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35623,7 +35626,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35829,7 +35832,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36447,7 +36450,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36653,7 +36656,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36859,7 +36862,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37065,7 +37068,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37477,7 +37480,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38095,7 +38098,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38301,7 +38304,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38507,7 +38510,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38919,7 +38922,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39000,7 +39003,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ183">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR183">
         <v>1.19</v>
@@ -39409,7 +39412,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ185">
         <v>0.8</v>
@@ -39743,7 +39746,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39949,7 +39952,7 @@
         <v>163</v>
       </c>
       <c r="P188" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q188">
         <v>2.75</v>
@@ -40439,7 +40442,7 @@
         <v>2</v>
       </c>
       <c r="AP190">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ190">
         <v>1.8</v>
@@ -40567,7 +40570,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40648,7 +40651,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ191">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR191">
         <v>1.6</v>
@@ -41185,7 +41188,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41803,7 +41806,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42215,7 +42218,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42421,7 +42424,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42627,7 +42630,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43039,7 +43042,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43451,7 +43454,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43863,7 +43866,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44069,7 +44072,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44432,6 +44435,212 @@
       </c>
       <c r="BP209">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7492365</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45681.69791666666</v>
+      </c>
+      <c r="F210">
+        <v>22</v>
+      </c>
+      <c r="G210" t="s">
+        <v>83</v>
+      </c>
+      <c r="H210" t="s">
+        <v>76</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210">
+        <v>2</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>2</v>
+      </c>
+      <c r="O210" t="s">
+        <v>228</v>
+      </c>
+      <c r="P210" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q210">
+        <v>2.75</v>
+      </c>
+      <c r="R210">
+        <v>2.05</v>
+      </c>
+      <c r="S210">
+        <v>4.33</v>
+      </c>
+      <c r="T210">
+        <v>1.5</v>
+      </c>
+      <c r="U210">
+        <v>2.5</v>
+      </c>
+      <c r="V210">
+        <v>3.4</v>
+      </c>
+      <c r="W210">
+        <v>1.3</v>
+      </c>
+      <c r="X210">
+        <v>10</v>
+      </c>
+      <c r="Y210">
+        <v>1.06</v>
+      </c>
+      <c r="Z210">
+        <v>2.06</v>
+      </c>
+      <c r="AA210">
+        <v>3.27</v>
+      </c>
+      <c r="AB210">
+        <v>4.1</v>
+      </c>
+      <c r="AC210">
+        <v>1.09</v>
+      </c>
+      <c r="AD210">
+        <v>8</v>
+      </c>
+      <c r="AE210">
+        <v>1.44</v>
+      </c>
+      <c r="AF210">
+        <v>2.8</v>
+      </c>
+      <c r="AG210">
+        <v>2.25</v>
+      </c>
+      <c r="AH210">
+        <v>1.57</v>
+      </c>
+      <c r="AI210">
+        <v>1.95</v>
+      </c>
+      <c r="AJ210">
+        <v>1.8</v>
+      </c>
+      <c r="AK210">
+        <v>1.25</v>
+      </c>
+      <c r="AL210">
+        <v>1.33</v>
+      </c>
+      <c r="AM210">
+        <v>1.75</v>
+      </c>
+      <c r="AN210">
+        <v>1</v>
+      </c>
+      <c r="AO210">
+        <v>0.9</v>
+      </c>
+      <c r="AP210">
+        <v>1.18</v>
+      </c>
+      <c r="AQ210">
+        <v>0.82</v>
+      </c>
+      <c r="AR210">
+        <v>1.04</v>
+      </c>
+      <c r="AS210">
+        <v>1.08</v>
+      </c>
+      <c r="AT210">
+        <v>2.12</v>
+      </c>
+      <c r="AU210">
+        <v>7</v>
+      </c>
+      <c r="AV210">
+        <v>2</v>
+      </c>
+      <c r="AW210">
+        <v>12</v>
+      </c>
+      <c r="AX210">
+        <v>5</v>
+      </c>
+      <c r="AY210">
+        <v>23</v>
+      </c>
+      <c r="AZ210">
+        <v>7</v>
+      </c>
+      <c r="BA210">
+        <v>6</v>
+      </c>
+      <c r="BB210">
+        <v>3</v>
+      </c>
+      <c r="BC210">
+        <v>9</v>
+      </c>
+      <c r="BD210">
+        <v>1.66</v>
+      </c>
+      <c r="BE210">
+        <v>6.5</v>
+      </c>
+      <c r="BF210">
+        <v>2.48</v>
+      </c>
+      <c r="BG210">
+        <v>1.32</v>
+      </c>
+      <c r="BH210">
+        <v>3.05</v>
+      </c>
+      <c r="BI210">
+        <v>1.55</v>
+      </c>
+      <c r="BJ210">
+        <v>2.25</v>
+      </c>
+      <c r="BK210">
+        <v>1.9</v>
+      </c>
+      <c r="BL210">
+        <v>1.78</v>
+      </c>
+      <c r="BM210">
+        <v>2.4</v>
+      </c>
+      <c r="BN210">
+        <v>1.49</v>
+      </c>
+      <c r="BO210">
+        <v>3.15</v>
+      </c>
+      <c r="BP210">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
